--- a/Data/IP_DPSP.xlsx
+++ b/Data/IP_DPSP.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,41 +472,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which part of the Indian Constitution deals with Directive Principles of State Policy?</t>
+          <t>Which of the following is a Gandhian Principle under DPSP?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Part II</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>Organization of village panchayats</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Uniform civil code</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Part V</t>
+          <t>Separation of judiciary from executive</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Organization of village panchayats</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Deals with guidelines for the State in governance.</t>
+          <t>Focuses on decentralization.</t>
         </is>
       </c>
     </row>
@@ -592,331 +592,331 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution mentions the application of DPSP?</t>
+          <t>Which Article directs the State to ensure health and strength of workers?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Article 31</t>
+          <t>Article 39(b)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Article 36</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Article 37</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Article 37</t>
+          <t>Article 39(b)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>States that DPSPs are non-justiciable.</t>
+          <t>Focuses on workers' health and strength.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which directive principle aims at providing free legal aid to the poor?</t>
+          <t>Directive Principles do NOT cover which of the following?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Environmental protection</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Right to property</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Promotion of cottage industries</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Uniform Civil Code</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Right to property</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ensures justice is not denied due to economic or other disabilities.</t>
+          <t>It is a Fundamental Right until 44th amendment, then removed.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Promotion of international peace and security is mentioned in which Article?</t>
+          <t>The Directive Principles aim to establish which type of state?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Welfare State</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Socialist State</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Secular State</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Article 53</t>
+          <t>Federal State</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Welfare State</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Guides India to promote global peace.</t>
+          <t>DPSPs guide India to be a welfare state.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DPSPs are meant for</t>
+          <t>Which Article of the Constitution says that the State shall take steps to separate the judiciary from the executive?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Central Government only</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>State Government only</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Both Centre and State</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Only Judiciary</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Both Centre and State</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>They apply to all levels of government.</t>
+          <t>Ensures independence of judiciary.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which of the following is a Gandhian principle under DPSP?</t>
+          <t>The principle of 'Promotion of international peace and security' is under which Article?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Equal pay for equal work</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Organization of Village Panchayats</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Uniform civil code</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Organization of Village Panchayats</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reflects Gandhi’s ideals.</t>
+          <t>Guides India’s foreign policy toward peace.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which Article relates to the Uniform Civil Code?</t>
+          <t>Which Article of the Indian Constitution directs the State to promote educational and economic interests of Scheduled Castes and Scheduled Tribes?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Article 46</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Article 45</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Article 44</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Article 45</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Article 47</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>Article 46</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Article 47</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Article 44</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Advises the State to secure a uniform civil code for citizens.</t>
+          <t>It aims at upliftment of SC/ST communities.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which of the following is not a DPSP?</t>
+          <t>Directive Principles are enforceable by</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Promotion of cottage industries</t>
+          <t>Courts</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Equal pay for equal work</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>The Executive</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Prohibition of intoxicating drinks</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>It is a Fundamental Right (Article 21A).</t>
+          <t>DPSPs are non-justiciable guidelines.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Directive Principles aim to establish</t>
+          <t>The Directive Principles are mainly inspired by the constitution of which country?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Political democracy</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Social democracy</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Religious democracy</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Economic democracy</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Social democracy</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>They promote social and economic justice.</t>
+          <t>Directive Principles are based on the Irish Constitution.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which Article encourages the State to promote educational interests of Scheduled Castes and Tribes?</t>
+          <t>Which Article directs the State to improve public health?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -941,132 +941,132 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Focuses on education and economic upliftment of SCs/STs.</t>
+          <t>Obliges State to raise nutrition and public health standards.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which directive speaks about organizing agriculture and animal husbandry on modern lines?</t>
+          <t>Which Article empowers the State to take steps for early childhood care?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 43A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Encourages scientific agriculture and animal care.</t>
+          <t>Focuses on providing free and compulsory education for children below six.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The idea of DPSP is to</t>
+          <t>Which of the following is a fundamental duty, not a Directive Principle?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ensure legal justice</t>
+          <t>Promoting international peace</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ensure rule of law</t>
+          <t>Protecting environment</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Establish a welfare state</t>
+          <t>Developing scientific temper</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Limit the power of Parliament</t>
+          <t>Respecting the Constitution</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Establish a welfare state</t>
+          <t>Respecting the Constitution</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DPSPs guide the State to build a just society.</t>
+          <t>Fundamental duties are under Part IVA.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which Article directs the State to improve public health?</t>
+          <t>Which principle under DPSPs directs the State to protect monuments of historical importance?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Article 48</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>Article 46</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Article 47</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Obliges State to raise nutrition and public health standards.</t>
+          <t>Protects cultural heritage.</t>
         </is>
       </c>
     </row>
@@ -1112,536 +1112,536 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which of these is a newly added DPSP?</t>
+          <t>The Directive Principle on ‘Promotion of international peace and security’ is under which Article?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Free legal aid</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Promotion of cooperative societies</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Uniform Civil Code</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Promotion of cooperative societies</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Inserted by 97th Amendment.</t>
+          <t>Guides India’s foreign policy.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>How many Articles are there in Part IV of the Constitution?</t>
+          <t>Which Article of the Constitution directs the State to raise the level of nutrition and standard of living?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Articles 36–50</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Articles 30–49</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Articles 39–52</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Articles 41–53</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Articles 36–50</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Total of 15 articles dealing with DPSPs.</t>
+          <t>Focuses on improving nutrition, public health, and standard of living.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which of these is not classified under Gandhian principles?</t>
+          <t>Which Article directs the State to protect monuments of historical importance?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cottage industries</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Panchayati Raj</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Prohibition of intoxicating drinks</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>It is a Liberal-Intellectual principle.</t>
+          <t>Preservation of cultural heritage.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which Article directs the State to provide early childhood care?</t>
+          <t>The Directive Principles are contained in which schedule of the Constitution?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>First Schedule</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Second Schedule</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Third Schedule</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Not in any schedule</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Not in any schedule</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Provision for children below 6 years.</t>
+          <t>They form Part IV of the Constitution.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>In which case did the Supreme Court declare that DPSPs are fundamental in governance?</t>
+          <t>Which Article directs the State to provide free and compulsory education to children?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Golaknath case</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Minerva Mills case</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Keshavananda Bharati case</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Champakam Dorairajan case</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Minerva Mills case</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Reiterated the importance of DPSPs.</t>
+          <t>Focuses on early childhood education.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which of the following DPSPs was added by the 42nd Amendment?</t>
+          <t>Which Article says the State shall provide free legal aid?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Equal pay for equal work</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Free legal aid</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Living wage for workers</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Free legal aid</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Introduced in Article 39A.</t>
+          <t>Guarantees legal assistance for the poor.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>What is the significance of DPSPs in governance?</t>
+          <t>Which Article encourages the promotion of cooperative societies?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>They are judicial orders</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>They limit legislative power</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>They serve as moral guidelines</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>They replace Fundamental Rights</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>They serve as moral guidelines</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Help the State frame just policies.</t>
+          <t>Inserted by the 97th Amendment.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which principle under DPSP reflects economic justice?</t>
+          <t>Which part of the Indian Constitution deals with Directive Principles of State Policy?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Free legal aid</t>
+          <t>Part II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Promotion of equal justice</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Organization of village panchayats</t>
+          <t>Part V</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Promotion of equal justice</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Ensures fairness in law and access to courts.</t>
+          <t>Deals with guidelines for the State in governance.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which principle is related to environment protection under DPSPs?</t>
+          <t>Which principle under DPSP reflects economic justice?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Free legal aid</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Promotion of equal justice</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Article 48A</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Organization of village panchayats</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Article 48A</t>
+          <t>Promotion of equal justice</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Inserted by 42nd Amendment, directs State to protect environment.</t>
+          <t>Ensures fairness in law and access to courts.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution directs the State to raise the level of nutrition and standard of living?</t>
+          <t>How many Articles are there in Part IV of the Constitution?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Articles 36–50</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Articles 30–49</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Articles 39–52</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Articles 41–53</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Articles 36–50</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Focuses on improving nutrition, public health, and standard of living.</t>
+          <t>Total of 15 articles dealing with DPSPs.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Directive Principles are mainly inspired by the constitution of which country?</t>
+          <t>Directive Principles are enforceable</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Only by Supreme Court</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Only by High Courts</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>By Parliament</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Not enforceable in courts</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Not enforceable in courts</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Directive Principles are based on the Irish Constitution.</t>
+          <t>They guide the State but are not legally enforceable.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which of the following is a fundamental duty, not a Directive Principle?</t>
+          <t>Which Article provides the directive for equal pay for equal work for men and women?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Promoting international peace</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Protecting environment</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Developing scientific temper</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Respecting the Constitution</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Respecting the Constitution</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Fundamental duties are under Part IVA.</t>
+          <t>Promotes gender equality in wages.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Directive Principles aim to establish which type of state?</t>
+          <t>Which principle is related to environment protection under DPSPs?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Welfare State</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Socialist State</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Secular State</t>
+          <t>Article 48A</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Federal State</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Welfare State</t>
+          <t>Article 48A</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>DPSPs guide India to be a welfare state.</t>
+          <t>Inserted by 42nd Amendment, directs State to protect environment.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which Article empowers the State to take steps for early childhood care?</t>
+          <t>The Directive Principle regarding the promotion of cooperative societies is mentioned in</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Article 43A</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1651,422 +1651,422 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Focuses on providing free and compulsory education for children below six.</t>
+          <t>Added by 97th Amendment.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which Article mandates the State to secure just and humane conditions of work?</t>
+          <t>Which Article mandates free legal aid to ensure justice for all?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>Article 40</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Article 41</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>Article 42</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Article 43</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Article 44</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Ensures humane working conditions and maternity benefits.</t>
+          <t>Ensures access to justice for the poor.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which Article mentions equal pay for equal work for both men and women?</t>
+          <t>Which of these is not classified under Gandhian principles?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>Cottage industries</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Panchayati Raj</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Prohibition of intoxicating drinks</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Ensures gender equality in wages.</t>
+          <t>It is a Liberal-Intellectual principle.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which of the following Articles talks about separation of judiciary from executive?</t>
+          <t>Which Article emphasizes the duty of the State to promote the educational and economic interests of Scheduled Castes, Scheduled Tribes, and other weaker sections?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Separation to ensure judicial independence.</t>
+          <t>Focuses on upliftment of marginalized groups.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DPSPs are enforceable by which body?</t>
+          <t>Which principle under DPSP relates to raising the standard of living and public health?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>High Court</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>DPSPs are non-justiciable.</t>
+          <t>Improves nutrition and health standards.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which Article promotes the welfare of the weaker sections of society?</t>
+          <t>Which Article directs the State to organize agriculture and animal husbandry on modern and scientific lines?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>Article 51</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>Article 48</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Article 46</t>
-        </is>
-      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Focuses on educational and economic interests of Scheduled Castes and Tribes.</t>
+          <t>Promotes scientific agriculture.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Directive Principles do NOT cover which of the following?</t>
+          <t>Which Article in the Indian Constitution directs the State to separate the judiciary from the executive?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Environmental protection</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Right to property</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Promotion of cottage industries</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Uniform Civil Code</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Right to property</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>It is a Fundamental Right until 44th amendment, then removed.</t>
+          <t>Ensures judicial independence and impartiality.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which Amendment added Article 48A on environmental protection?</t>
+          <t>Which Directive Principle calls for free and compulsory education for children?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Inserted the directive on environment protection.</t>
+          <t>Cares for early childhood education.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which Article urges the State to organize village panchayats?</t>
+          <t>Which Article directs the State to protect monuments of historical importance?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Promotes decentralization through local self-government.</t>
+          <t>Preserves cultural heritage.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which Article calls for securing just and humane conditions of work?</t>
+          <t>DPSPs are meant for</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Central Government only</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>State Government only</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Both Centre and State</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Article 37</t>
+          <t>Only Judiciary</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Both Centre and State</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Includes maternity relief provisions.</t>
+          <t>They apply to all levels of government.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which principle under DPSPs directs the State to protect monuments of historical importance?</t>
+          <t>Which of the following DPSPs was added by the 42nd Amendment?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Equal pay for equal work</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Free legal aid</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Living wage for workers</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Free legal aid</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Protects cultural heritage.</t>
+          <t>Introduced in Article 39A.</t>
         </is>
       </c>
     </row>
@@ -2112,106 +2112,106 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which Directive Principle deals with providing adequate means of livelihood?</t>
+          <t>Which Article of the Constitution mentions the application of DPSP?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Article 31</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 36</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>Article 37</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>Article 40</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Article 38</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Article 37</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Ensures citizens have the right to work and livelihood.</t>
+          <t>States that DPSPs are non-justiciable.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which Article directs the State to ensure health and strength of workers?</t>
+          <t>Which directive principle aims at providing free legal aid to the poor?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Article 39(b)</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>Article 39A</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>Article 41</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Article 42</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Article 43</t>
-        </is>
-      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Article 39(b)</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Focuses on workers' health and strength.</t>
+          <t>Ensures justice is not denied due to economic or other disabilities.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which Article requires the State to ensure the participation of workers in management?</t>
+          <t>Which Article provides that the State shall promote the welfare of workers?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Article 43A</t>
+          <t>Article 38</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2221,117 +2221,117 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Article 43A</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Added by 42nd Amendment.</t>
+          <t>Focuses on social security and public assistance.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which Article calls for the State to promote equal justice and free legal aid?</t>
+          <t>Which Amendment introduced the Directive Principle relating to environment protection?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Ensures justice for economically weak sections.</t>
+          <t>Added Article 48A for environmental protection.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Directive Principles are contained in which schedule of the Constitution?</t>
+          <t>Are Directive Principles superior to Fundamental Rights?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>First Schedule</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Second Schedule</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Third Schedule</t>
+          <t>Depends on the case</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Not in any schedule</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Not in any schedule</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>They form Part IV of the Constitution.</t>
+          <t>Fundamental Rights have supremacy over DPSPs.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The principle of 'Promotion of international peace and security' is under which Article?</t>
+          <t>Which Article directs the State to promote the educational and economic interests of Scheduled Castes and Scheduled Tribes?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2341,162 +2341,162 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Guides India’s foreign policy toward peace.</t>
+          <t>Uplifts marginalized communities.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which Article calls upon the State to endeavor to promote the welfare of workers?</t>
+          <t>Which Directive Principle mandates protection of monuments and objects of national importance?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Focuses on social security and public assistance.</t>
+          <t>Protects cultural heritage.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which Article says that the State shall not discriminate against any citizen on grounds of religion, race, caste, sex or place of birth?</t>
+          <t>Which amendment added the Directive Principle relating to environment protection?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Article 14</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Article 15</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Article 16</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Article 17</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Article 15</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>It is a Fundamental Right, not a DPSP.</t>
+          <t>Inserted Article 48A.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Are Directive Principles superior to Fundamental Rights?</t>
+          <t>The Directive Principles are classified under which part of the Constitution?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Depends on the case</t>
+          <t>Part V</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Not mentioned</t>
+          <t>Part VI</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Fundamental Rights have supremacy over DPSPs.</t>
+          <t>Contains Articles 36 to 51.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which Article of the Indian Constitution directs the State to promote educational and economic interests of Scheduled Castes and Scheduled Tribes?</t>
+          <t>Which Article encourages the State to promote educational interests of Scheduled Castes and Tribes?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>Article 45</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>Article 46</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Article 45</t>
-        </is>
-      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2506,777 +2506,777 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>It aims at upliftment of SC/ST communities.</t>
+          <t>Focuses on education and economic upliftment of SCs/STs.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Directive Principle of 'Uniform Civil Code' aims to promote</t>
+          <t>Which Article calls for the State to promote equal justice and free legal aid?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Secularism</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Legal Uniformity</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Religious Harmony</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Federalism</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Legal Uniformity</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>To have one law for all citizens irrespective of religion.</t>
+          <t>Ensures justice for economically weak sections.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which Article directs the State to organize agriculture and animal husbandry on modern lines?</t>
+          <t>Which Article deals with the promotion of cottage industries in rural areas?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>It encourages scientific farming and animal care.</t>
+          <t>Supports rural self-employment.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a Directive Principle?</t>
+          <t>The Directive Principle related to free legal aid to the poor is found in which Article?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Right to Freedom of Speech</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Provision for free legal aid</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Promotion of cottage industries</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Protection of monuments</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Right to Freedom of Speech</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>This is a Fundamental Right.</t>
+          <t>Ensures justice access to the marginalized.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The Directive Principles are classified under which part of the Constitution?</t>
+          <t>Which Article calls for securing just and humane conditions of work?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Part V</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Part VI</t>
+          <t>Article 37</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Contains Articles 36 to 51.</t>
+          <t>Includes maternity relief provisions.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which Article directs the State to raise the level of nutrition and public health?</t>
+          <t>Which directive speaks about organizing agriculture and animal husbandry on modern lines?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
+          <t>Article 50</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>Article 48</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Article 47</t>
-        </is>
-      </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>It emphasizes improvement of public health.</t>
+          <t>Encourages scientific agriculture and animal care.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution says that the State shall take steps to separate the judiciary from the executive?</t>
+          <t>Which Article calls for just and humane conditions of work and maternity relief?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Ensures independence of judiciary.</t>
+          <t>Ensures worker welfare.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Who among the following is primarily responsible for implementing Directive Principles?</t>
+          <t>Which Directive Principle calls for the separation of judiciary from the executive?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>The government must act according to DPSPs.</t>
+          <t>Ensures judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Directive Principle related to free legal aid to the poor is found in which Article?</t>
+          <t>Which of the following Articles is related to providing just and humane conditions of work?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
+          <t>Article 44</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
           <t>Article 42</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Article 39A</t>
-        </is>
-      </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Ensures justice access to the marginalized.</t>
+          <t>Also includes maternity benefits.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which amendment added the Directive Principle relating to environment protection?</t>
+          <t>Which Article calls upon the State to endeavor to promote the welfare of workers?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Inserted Article 48A.</t>
+          <t>Focuses on social security and public assistance.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which Article directs the State to provide early childhood care and education to children below the age of six?</t>
+          <t>Which of the following is NOT a Directive Principle?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Right to Freedom of Speech</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Provision for free legal aid</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Promotion of cottage industries</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Protection of monuments</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Right to Freedom of Speech</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Focus on child welfare.</t>
+          <t>This is a Fundamental Right.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Directive Principle on ‘Promotion of international peace and security’ is under which Article?</t>
+          <t>DPSPs are enforceable by which body?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>High Court</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Guides India’s foreign policy.</t>
+          <t>DPSPs are non-justiciable.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Directive Principles are</t>
+          <t>Which Directive Principle deals with providing adequate means of livelihood?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fundamental rights</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Non-justiciable guidelines</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Justiciable laws</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>International treaties</t>
+          <t>Article 38</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Non-justiciable guidelines</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>They are guidelines for governance.</t>
+          <t>Ensures citizens have the right to work and livelihood.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which Article deals with the promotion of cottage industries in rural areas?</t>
+          <t>Which Article requires the State to ensure the participation of workers in management?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 43A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>Article 43B</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>Article 44</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Article 45</t>
-        </is>
-      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 43A</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Supports rural self-employment.</t>
+          <t>Added by 42nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Directive Principle on providing adequate livelihood for citizens is found in which Article?</t>
+          <t>Which Article deals with the promotion of cottage industries in rural areas?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Ensures right to work and livelihood.</t>
+          <t>Encourages rural self-employment and handicrafts.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which of the following Articles is related to providing just and humane conditions of work?</t>
+          <t>Which Article promotes the welfare of the weaker sections of society?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Also includes maternity benefits.</t>
+          <t>Focuses on educational and economic interests of Scheduled Castes and Tribes.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Directive Principles are enforceable</t>
+          <t>Which Article mandates the State to secure just and humane conditions of work?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Only by Supreme Court</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Only by High Courts</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>By Parliament</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Not enforceable in courts</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Not enforceable in courts</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>They guide the State but are not legally enforceable.</t>
+          <t>Ensures humane working conditions and maternity benefits.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which Article promotes equal pay for equal work for both men and women?</t>
+          <t>What is the significance of DPSPs in governance?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>They are judicial orders</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>They limit legislative power</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>They serve as moral guidelines</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>They replace Fundamental Rights</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>They serve as moral guidelines</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Ensures gender equality in wages.</t>
+          <t>Help the State frame just policies.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Directive Principle regarding the promotion of cooperative societies is mentioned in</t>
+          <t>The Directive Principle regarding organization of village panchayats is in</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>Article 42</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Article 43</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>Article 44</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Article 46</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Article 39</t>
-        </is>
-      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Added by 97th Amendment.</t>
+          <t>Encourages local self-government.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which Article directs the State to protect monuments of historical importance?</t>
+          <t>Which Article directs the State to provide early childhood care?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Preserves cultural heritage.</t>
+          <t>Provision for children below 6 years.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which Article directs the State to secure a uniform civil code?</t>
+          <t>Which Article relates to the Uniform Civil Code?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3306,107 +3306,107 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Promotes legal uniformity across religions.</t>
+          <t>Advises the State to secure a uniform civil code for citizens.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which principle under DPSP relates to raising the standard of living and public health?</t>
+          <t>Which of these is a newly added DPSP?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Free legal aid</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Promotion of cooperative societies</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Uniform Civil Code</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Promotion of cooperative societies</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Improves nutrition and health standards.</t>
+          <t>Inserted by 97th Amendment.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which of the following is a Gandhian Principle under DPSP?</t>
+          <t>Which Directive Principle relates to the promotion of scientific temper and humanism?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Article 51A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Organization of village panchayats</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Uniform civil code</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Separation of judiciary from executive</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Organization of village panchayats</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Focuses on decentralization.</t>
+          <t>Promotes rational thinking and tolerance.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which Directive Principle calls for free and compulsory education for children?</t>
+          <t>Which Article promotes equal pay for equal work for both men and women?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3416,682 +3416,682 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Cares for early childhood education.</t>
+          <t>Ensures gender equality in wages.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which Article directs the State to promote the educational and economic interests of Scheduled Castes and Scheduled Tribes?</t>
+          <t>The Directive Principle on providing adequate livelihood for citizens is found in which Article?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Uplifts marginalized communities.</t>
+          <t>Ensures right to work and livelihood.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which Article in the Indian Constitution directs the State to separate the judiciary from the executive?</t>
+          <t>The Directive Principle which calls for securing just and humane conditions of work is</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
+          <t>Article 41</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Article 42</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Article 43</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>Article 44</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Article 45</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Article 50</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Article 51</t>
-        </is>
-      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Ensures judicial independence and impartiality.</t>
+          <t>Includes maternity relief provisions.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which Article provides that the State shall promote the welfare of workers?</t>
+          <t>Which Article urges the State to organize village panchayats?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Article 38</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>Article 44</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Article 40</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>Article 39</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Article 41</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Article 42</t>
-        </is>
-      </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Focuses on social security and public assistance.</t>
+          <t>Promotes decentralization through local self-government.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Directive Principle which calls for securing just and humane conditions of work is</t>
+          <t>Which Article says that the State shall not discriminate against any citizen on grounds of religion, race, caste, sex or place of birth?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 14</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 15</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 16</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 17</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 15</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Includes maternity relief provisions.</t>
+          <t>It is a Fundamental Right, not a DPSP.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which Article directs the State to provide adequate means of livelihood to its citizens?</t>
+          <t>Directive Principles are contained in which Part of the Constitution?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Part V</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Part VI</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Guarantees the right to work and livelihood.</t>
+          <t>Comprising Articles 36 to 51.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Which Article deals with the promotion of cottage industries in rural areas?</t>
+          <t>Which of the following is NOT a Directive Principle of State Policy?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Right to Property</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Promotion of cottage industries</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Uniform Civil Code</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Organization of Village Panchayats</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Right to Property</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Encourages rural self-employment and handicrafts.</t>
+          <t>It was removed from Fundamental Rights and is not a DPSP.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a Directive Principle of State Policy?</t>
+          <t>Directive Principles aim to establish</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Right to Property</t>
+          <t>Political democracy</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Promotion of cottage industries</t>
+          <t>Social democracy</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Uniform Civil Code</t>
+          <t>Religious democracy</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Organization of Village Panchayats</t>
+          <t>Economic democracy</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Right to Property</t>
+          <t>Social democracy</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>It was removed from Fundamental Rights and is not a DPSP.</t>
+          <t>They promote social and economic justice.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which Article urges the State to raise the level of nutrition and public health?</t>
+          <t>Which Article directs the State to secure a uniform civil code?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
+          <t>Article 44</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Article 43</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Article 42</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>Article 45</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Article 46</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Article 47</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Article 48</t>
-        </is>
-      </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Focuses on health and nutrition improvement.</t>
+          <t>Promotes legal uniformity across religions.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which Article mandates free legal aid to ensure justice for all?</t>
+          <t>Which Article urges the State to raise the level of nutrition and public health?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Ensures access to justice for the poor.</t>
+          <t>Focuses on health and nutrition improvement.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Directive Principles are contained in which Part of the Constitution?</t>
+          <t>Which Article provides for the promotion of international peace and security?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Part V</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Part VI</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Comprising Articles 36 to 51.</t>
+          <t>Guides India's foreign policy towards peace.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Which Article directs the State to protect monuments of historical importance?</t>
+          <t>Directive Principles are</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Fundamental rights</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Non-justiciable guidelines</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Justiciable laws</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>International treaties</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Non-justiciable guidelines</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Preservation of cultural heritage.</t>
+          <t>They are guidelines for governance.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which Article provides for the promotion of international peace and security?</t>
+          <t>Which Amendment added Article 48A on environmental protection?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Article 53</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Guides India's foreign policy towards peace.</t>
+          <t>Inserted the directive on environment protection.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The Directive Principle regarding organization of village panchayats is in</t>
+          <t>Which Article directs the State to raise the level of nutrition and public health?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Encourages local self-government.</t>
+          <t>It emphasizes improvement of public health.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which Directive Principle relates to the promotion of scientific temper and humanism?</t>
+          <t>Which Article directs the State to provide adequate means of livelihood to its citizens?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Article 51A</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Promotes rational thinking and tolerance.</t>
+          <t>Guarantees the right to work and livelihood.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which Article emphasizes the duty of the State to promote the educational and economic interests of Scheduled Castes, Scheduled Tribes, and other weaker sections?</t>
+          <t>The Directive Principle of 'Uniform Civil Code' aims to promote</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Secularism</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Legal Uniformity</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Religious Harmony</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Federalism</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Legal Uniformity</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Focuses on upliftment of marginalized groups.</t>
+          <t>To have one law for all citizens irrespective of religion.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which Amendment introduced the Directive Principle relating to environment protection?</t>
+          <t>Promotion of international peace and security is mentioned in which Article?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Added Article 48A for environmental protection.</t>
+          <t>Guides India to promote global peace.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which Article directs the State to provide free and compulsory education to children?</t>
+          <t>Which Article mentions equal pay for equal work for both men and women?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4101,67 +4101,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Focuses on early childhood education.</t>
+          <t>Ensures gender equality in wages.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which Article provides the directive for equal pay for equal work for men and women?</t>
+          <t>Which Article states that the State shall endeavor to raise the level of nutrition and improve public health?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Promotes gender equality in wages.</t>
+          <t>Promotes public health initiatives.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Directive Principles are enforceable by</t>
+          <t>Who among the following is primarily responsible for implementing Directive Principles?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Courts</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4171,272 +4171,272 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>The Executive</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>DPSPs are non-justiciable guidelines.</t>
+          <t>The government must act according to DPSPs.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which Article states that the State shall endeavor to raise the level of nutrition and improve public health?</t>
+          <t>Which of the following is not a DPSP?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Promotion of cottage industries</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Equal pay for equal work</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Prohibition of intoxicating drinks</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Promotes public health initiatives.</t>
+          <t>It is a Fundamental Right (Article 21A).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Which Article calls for just and humane conditions of work and maternity relief?</t>
+          <t>In which case did the Supreme Court declare that DPSPs are fundamental in governance?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Golaknath case</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Minerva Mills case</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Keshavananda Bharati case</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Champakam Dorairajan case</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Minerva Mills case</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Ensures worker welfare.</t>
+          <t>Reiterated the importance of DPSPs.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which Article encourages the promotion of cooperative societies?</t>
+          <t>Which of the following is a Gandhian principle under DPSP?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Equal pay for equal work</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Organization of Village Panchayats</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Uniform civil code</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Organization of Village Panchayats</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Inserted by the 97th Amendment.</t>
+          <t>Reflects Gandhi’s ideals.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which Directive Principle calls for the separation of judiciary from the executive?</t>
+          <t>Which Article directs the State to provide early childhood care and education to children below the age of six?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Ensures judicial independence.</t>
+          <t>Focus on child welfare.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which Article says the State shall provide free legal aid?</t>
+          <t>The idea of DPSP is to</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Ensure legal justice</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Ensure rule of law</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Establish a welfare state</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Limit the power of Parliament</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Establish a welfare state</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Guarantees legal assistance for the poor.</t>
+          <t>DPSPs guide the State to build a just society.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which Directive Principle mandates protection of monuments and objects of national importance?</t>
+          <t>Which of the following Articles talks about separation of judiciary from executive?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t>Article 50</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Article 51</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>Article 49</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>Article 50</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Article 51</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Article 49</t>
-        </is>
-      </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Protects cultural heritage.</t>
+          <t>Separation to ensure judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which Article directs the State to organize agriculture and animal husbandry on modern and scientific lines?</t>
+          <t>Which Article directs the State to organize agriculture and animal husbandry on modern lines?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Promotes scientific agriculture.</t>
+          <t>It encourages scientific farming and animal care.</t>
         </is>
       </c>
     </row>

--- a/Data/IP_DPSP.xlsx
+++ b/Data/IP_DPSP.xlsx
@@ -472,761 +472,761 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which of the following is a Gandhian Principle under DPSP?</t>
+          <t>Which of the following DPSPs was added by the 42nd Amendment?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Equal pay for equal work</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Free legal aid</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Promotion of international peace</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Organization of village panchayats</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Uniform civil code</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Separation of judiciary from executive</t>
+          <t>Living wage for workers</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Organization of village panchayats</t>
+          <t>Free legal aid</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Focuses on decentralization.</t>
+          <t>Introduced in Article 39A.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The concept of DPSP was borrowed from which country?</t>
+          <t>Directive Principles are</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Fundamental rights</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Non-justiciable guidelines</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Justiciable laws</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>International treaties</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Non-justiciable guidelines</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>India adopted DPSP from the Irish Constitution.</t>
+          <t>They are guidelines for governance.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DPSPs are</t>
+          <t>Which of the following principles is classified as a Liberal-Intellectual Principle?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Justiciable</t>
+          <t>Promotion of cooperative societies</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Non-Justiciable</t>
+          <t>Separation of judiciary from executive</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Legally binding</t>
+          <t>Provision for early childhood care</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fundamental Rights</t>
+          <t>Promotion of educational interests</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Non-Justiciable</t>
+          <t>Separation of judiciary from executive</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>They are not enforceable by courts.</t>
+          <t>Aims at impartial justice system.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which Article directs the State to ensure health and strength of workers?</t>
+          <t>Which principle under DPSPs directs the State to protect monuments of historical importance?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Article 39(b)</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Article 39(b)</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Focuses on workers' health and strength.</t>
+          <t>Protects cultural heritage.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Directive Principles do NOT cover which of the following?</t>
+          <t>Directive Principles aim to establish</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Environmental protection</t>
+          <t>Political democracy</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Right to property</t>
+          <t>Social democracy</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Promotion of cottage industries</t>
+          <t>Religious democracy</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Uniform Civil Code</t>
+          <t>Economic democracy</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Right to property</t>
+          <t>Social democracy</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>It is a Fundamental Right until 44th amendment, then removed.</t>
+          <t>They promote social and economic justice.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Directive Principles aim to establish which type of state?</t>
+          <t>Which Article says that the State shall not discriminate against any citizen on grounds of religion, race, caste, sex or place of birth?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Welfare State</t>
+          <t>Article 14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Socialist State</t>
+          <t>Article 15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Secular State</t>
+          <t>Article 16</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Federal State</t>
+          <t>Article 17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Welfare State</t>
+          <t>Article 15</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DPSPs guide India to be a welfare state.</t>
+          <t>It is a Fundamental Right, not a DPSP.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution says that the State shall take steps to separate the judiciary from the executive?</t>
+          <t>Which Article directs the State to organize agriculture and animal husbandry on modern and scientific lines?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Article 48</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Article 49</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Article 50</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Article 51</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Article 49</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Article 48</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Article 50</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Ensures independence of judiciary.</t>
+          <t>Promotes scientific agriculture.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The principle of 'Promotion of international peace and security' is under which Article?</t>
+          <t>Which Directive Principle calls for free and compulsory education for children?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Guides India’s foreign policy toward peace.</t>
+          <t>Cares for early childhood education.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which Article of the Indian Constitution directs the State to promote educational and economic interests of Scheduled Castes and Scheduled Tribes?</t>
+          <t>Which Article deals with the promotion of cottage industries in rural areas?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Article 43</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Article 44</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Article 45</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Article 46</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Article 45</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Article 44</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Article 47</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>It aims at upliftment of SC/ST communities.</t>
+          <t>Encourages rural self-employment and handicrafts.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Directive Principles are enforceable by</t>
+          <t>Which Article calls upon the State to endeavor to promote the welfare of workers?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Courts</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The Executive</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DPSPs are non-justiciable guidelines.</t>
+          <t>Focuses on social security and public assistance.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Directive Principles are mainly inspired by the constitution of which country?</t>
+          <t>The idea of DPSP is to</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Ensure legal justice</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Ensure rule of law</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Establish a welfare state</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Limit the power of Parliament</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Establish a welfare state</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Directive Principles are based on the Irish Constitution.</t>
+          <t>DPSPs guide the State to build a just society.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which Article directs the State to improve public health?</t>
+          <t>DPSPs are enforceable by which body?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>High Court</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Obliges State to raise nutrition and public health standards.</t>
+          <t>DPSPs are non-justiciable.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which Article empowers the State to take steps for early childhood care?</t>
+          <t>Which of the following is NOT a Directive Principle?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Article 43A</t>
+          <t>Right to Freedom of Speech</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Provision for free legal aid</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Promotion of cottage industries</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Protection of monuments</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Right to Freedom of Speech</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Focuses on providing free and compulsory education for children below six.</t>
+          <t>This is a Fundamental Right.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which of the following is a fundamental duty, not a Directive Principle?</t>
+          <t>Which Article provides for the promotion of international peace and security?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Promoting international peace</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Protecting environment</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Developing scientific temper</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Respecting the Constitution</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Respecting the Constitution</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fundamental duties are under Part IVA.</t>
+          <t>Guides India's foreign policy towards peace.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which principle under DPSPs directs the State to protect monuments of historical importance?</t>
+          <t>Which Article directs the State to provide adequate means of livelihood to its citizens?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Protects cultural heritage.</t>
+          <t>Guarantees the right to work and livelihood.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which of the following principles is classified as a Liberal-Intellectual Principle?</t>
+          <t>Which Article requires the State to ensure the participation of workers in management?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Promotion of cooperative societies</t>
+          <t>Article 43A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Separation of judiciary from executive</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Provision for early childhood care</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Promotion of educational interests</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Separation of judiciary from executive</t>
+          <t>Article 43A</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Aims at impartial justice system.</t>
+          <t>Added by 42nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Directive Principle on ‘Promotion of international peace and security’ is under which Article?</t>
+          <t>Which Article promotes equal pay for equal work for both men and women?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Guides India’s foreign policy.</t>
+          <t>Ensures gender equality in wages.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution directs the State to raise the level of nutrition and standard of living?</t>
+          <t>Directive Principles are contained in which Part of the Constitution?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Part V</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Part VI</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Focuses on improving nutrition, public health, and standard of living.</t>
+          <t>Comprising Articles 36 to 51.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which Article directs the State to protect monuments of historical importance?</t>
+          <t>The Directive Principles are mainly inspired by the constitution of which country?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Preservation of cultural heritage.</t>
+          <t>Directive Principles are based on the Irish Constitution.</t>
         </is>
       </c>
     </row>
@@ -1272,821 +1272,821 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which Article directs the State to provide free and compulsory education to children?</t>
+          <t>Which Article directs the State to organize agriculture and animal husbandry on modern lines?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Focuses on early childhood education.</t>
+          <t>It encourages scientific farming and animal care.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which Article says the State shall provide free legal aid?</t>
+          <t>Which Amendment introduced the Directive Principle relating to environment protection?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Guarantees legal assistance for the poor.</t>
+          <t>Added Article 48A for environmental protection.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which Article encourages the promotion of cooperative societies?</t>
+          <t>The principle of 'Promotion of international peace and security' is under which Article?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Inserted by the 97th Amendment.</t>
+          <t>Guides India’s foreign policy toward peace.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which part of the Indian Constitution deals with Directive Principles of State Policy?</t>
+          <t>What is the significance of DPSPs in governance?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Part II</t>
+          <t>They are judicial orders</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>They limit legislative power</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>They serve as moral guidelines</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Part V</t>
+          <t>They replace Fundamental Rights</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>They serve as moral guidelines</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Deals with guidelines for the State in governance.</t>
+          <t>Help the State frame just policies.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which principle under DPSP reflects economic justice?</t>
+          <t>Which directive speaks about organizing agriculture and animal husbandry on modern lines?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Free legal aid</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Promotion of equal justice</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Organization of village panchayats</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Promotion of equal justice</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Ensures fairness in law and access to courts.</t>
+          <t>Encourages scientific agriculture and animal care.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>How many Articles are there in Part IV of the Constitution?</t>
+          <t>Which Article encourages the promotion of cooperative societies?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Articles 36–50</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Articles 30–49</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Articles 39–52</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Articles 41–53</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Articles 36–50</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Total of 15 articles dealing with DPSPs.</t>
+          <t>Inserted by the 97th Amendment.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Directive Principles are enforceable</t>
+          <t>In which case did the Supreme Court declare that DPSPs are fundamental in governance?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Only by Supreme Court</t>
+          <t>Golaknath case</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Only by High Courts</t>
+          <t>Minerva Mills case</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>By Parliament</t>
+          <t>Keshavananda Bharati case</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Not enforceable in courts</t>
+          <t>Champakam Dorairajan case</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Not enforceable in courts</t>
+          <t>Minerva Mills case</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>They guide the State but are not legally enforceable.</t>
+          <t>Reiterated the importance of DPSPs.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which Article provides the directive for equal pay for equal work for men and women?</t>
+          <t>The Directive Principle regarding organization of village panchayats is in</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>Article 42</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Article 43</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Article 44</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>Article 40</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Article 41</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Article 42</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Article 39(d)</t>
-        </is>
-      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Promotes gender equality in wages.</t>
+          <t>Encourages local self-government.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which principle is related to environment protection under DPSPs?</t>
+          <t>Directive Principles do NOT cover which of the following?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Environmental protection</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Right to property</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Article 48A</t>
+          <t>Promotion of cottage industries</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Uniform Civil Code</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Article 48A</t>
+          <t>Right to property</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Inserted by 42nd Amendment, directs State to protect environment.</t>
+          <t>It is a Fundamental Right until 44th amendment, then removed.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Directive Principle regarding the promotion of cooperative societies is mentioned in</t>
+          <t>Which Directive Principle deals with providing adequate means of livelihood?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 38</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Added by 97th Amendment.</t>
+          <t>Ensures citizens have the right to work and livelihood.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which Article mandates free legal aid to ensure justice for all?</t>
+          <t>The Directive Principles are classified under which part of the Constitution?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Part V</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Part VI</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Ensures access to justice for the poor.</t>
+          <t>Contains Articles 36 to 51.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which of these is not classified under Gandhian principles?</t>
+          <t>Which of these is a newly added DPSP?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cottage industries</t>
+          <t>Free legal aid</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Promotion of cooperative societies</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Panchayati Raj</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Prohibition of intoxicating drinks</t>
+          <t>Uniform Civil Code</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Promotion of cooperative societies</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>It is a Liberal-Intellectual principle.</t>
+          <t>Inserted by 97th Amendment.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which Article emphasizes the duty of the State to promote the educational and economic interests of Scheduled Castes, Scheduled Tribes, and other weaker sections?</t>
+          <t>Which Article directs the State to promote voluntary formation of cooperative societies?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>Article 44</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Article 46</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Article 47</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Focuses on upliftment of marginalized groups.</t>
+          <t>Added by the 97th Amendment.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which principle under DPSP relates to raising the standard of living and public health?</t>
+          <t>The Directive Principle of 'Uniform Civil Code' aims to promote</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Secularism</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Legal Uniformity</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Religious Harmony</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Federalism</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Legal Uniformity</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Improves nutrition and health standards.</t>
+          <t>To have one law for all citizens irrespective of religion.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which Article directs the State to organize agriculture and animal husbandry on modern and scientific lines?</t>
+          <t>Which Article states that the State shall endeavor to raise the level of nutrition and improve public health?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Article 45</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Article 46</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Article 47</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>Article 48</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Article 49</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Article 50</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Article 51</t>
-        </is>
-      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Promotes scientific agriculture.</t>
+          <t>Promotes public health initiatives.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which Article in the Indian Constitution directs the State to separate the judiciary from the executive?</t>
+          <t>Which Article urges the State to organize village panchayats?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>Article 43</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>Article 44</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Article 45</t>
-        </is>
-      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Ensures judicial independence and impartiality.</t>
+          <t>Promotes decentralization through local self-government.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which Directive Principle calls for free and compulsory education for children?</t>
+          <t>Directive Principles are enforceable</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Only by Supreme Court</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Only by High Courts</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>By Parliament</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Not enforceable in courts</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Not enforceable in courts</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Cares for early childhood education.</t>
+          <t>They guide the State but are not legally enforceable.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which Article directs the State to protect monuments of historical importance?</t>
+          <t>The Directive Principle related to free legal aid to the poor is found in which Article?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Preserves cultural heritage.</t>
+          <t>Ensures justice access to the marginalized.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DPSPs are meant for</t>
+          <t>Which Article directs the State to protect monuments of historical importance?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Central Government only</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>State Government only</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Both Centre and State</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Only Judiciary</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Both Centre and State</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>They apply to all levels of government.</t>
+          <t>Preserves cultural heritage.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which of the following DPSPs was added by the 42nd Amendment?</t>
+          <t>How many Articles are there in Part IV of the Constitution?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Equal pay for equal work</t>
+          <t>Articles 36–50</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Free legal aid</t>
+          <t>Articles 30–49</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Articles 39–52</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Living wage for workers</t>
+          <t>Articles 41–53</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Free legal aid</t>
+          <t>Articles 36–50</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Introduced in Article 39A.</t>
+          <t>Total of 15 articles dealing with DPSPs.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which Article directs the State to promote voluntary formation of cooperative societies?</t>
+          <t>Which Article directs the State to provide early childhood care and education to children below the age of six?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2096,77 +2096,77 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Added by the 97th Amendment.</t>
+          <t>Focus on child welfare.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution mentions the application of DPSP?</t>
+          <t>DPSPs are meant for</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Article 31</t>
+          <t>Central Government only</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Article 36</t>
+          <t>State Government only</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Article 37</t>
+          <t>Both Centre and State</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Only Judiciary</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Article 37</t>
+          <t>Both Centre and State</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>States that DPSPs are non-justiciable.</t>
+          <t>They apply to all levels of government.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which directive principle aims at providing free legal aid to the poor?</t>
+          <t>Which Article provides the directive for equal pay for equal work for men and women?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2181,1052 +2181,1052 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Ensures justice is not denied due to economic or other disabilities.</t>
+          <t>Promotes gender equality in wages.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which Article provides that the State shall promote the welfare of workers?</t>
+          <t>Which Article calls for securing just and humane conditions of work?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Article 38</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>Article 41</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>Article 39</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Article 41</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>Article 37</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>Article 42</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Article 41</t>
-        </is>
-      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Focuses on social security and public assistance.</t>
+          <t>Includes maternity relief provisions.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which Amendment introduced the Directive Principle relating to environment protection?</t>
+          <t>Which Article directs the State to protect monuments of historical importance?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Added Article 48A for environmental protection.</t>
+          <t>Preservation of cultural heritage.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Are Directive Principles superior to Fundamental Rights?</t>
+          <t>Which Article directs the State to promote the educational and economic interests of Scheduled Castes and Scheduled Tribes?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Depends on the case</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Not mentioned</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fundamental Rights have supremacy over DPSPs.</t>
+          <t>Uplifts marginalized communities.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which Article directs the State to promote the educational and economic interests of Scheduled Castes and Scheduled Tribes?</t>
+          <t>Which of the following Articles is related to providing just and humane conditions of work?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Uplifts marginalized communities.</t>
+          <t>Also includes maternity benefits.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which Directive Principle mandates protection of monuments and objects of national importance?</t>
+          <t>Which Article encourages the State to promote educational interests of Scheduled Castes and Tribes?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>Article 45</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Article 46</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Article 47</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>Article 48</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Article 49</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Article 50</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Article 51</t>
-        </is>
-      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Protects cultural heritage.</t>
+          <t>Focuses on education and economic upliftment of SCs/STs.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which amendment added the Directive Principle relating to environment protection?</t>
+          <t>Which of the following is a Gandhian Principle under DPSP?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Organization of village panchayats</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Uniform civil code</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>Separation of judiciary from executive</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Organization of village panchayats</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Inserted Article 48A.</t>
+          <t>Focuses on decentralization.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Directive Principles are classified under which part of the Constitution?</t>
+          <t>Directive Principles are enforceable by</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>Courts</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Part V</t>
+          <t>The Executive</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Part VI</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Contains Articles 36 to 51.</t>
+          <t>DPSPs are non-justiciable guidelines.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which Article encourages the State to promote educational interests of Scheduled Castes and Tribes?</t>
+          <t>Which directive principle aims at providing free legal aid to the poor?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Focuses on education and economic upliftment of SCs/STs.</t>
+          <t>Ensures justice is not denied due to economic or other disabilities.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which Article calls for the State to promote equal justice and free legal aid?</t>
+          <t>DPSPs are</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Justiciable</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Non-Justiciable</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Legally binding</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Fundamental Rights</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Non-Justiciable</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Ensures justice for economically weak sections.</t>
+          <t>They are not enforceable by courts.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which Article deals with the promotion of cottage industries in rural areas?</t>
+          <t>Which Article of the Constitution directs the State to raise the level of nutrition and standard of living?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Supports rural self-employment.</t>
+          <t>Focuses on improving nutrition, public health, and standard of living.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Directive Principle related to free legal aid to the poor is found in which Article?</t>
+          <t>Which of the following is a Gandhian principle under DPSP?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Equal pay for equal work</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Organization of Village Panchayats</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Uniform civil code</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Organization of Village Panchayats</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Ensures justice access to the marginalized.</t>
+          <t>Reflects Gandhi’s ideals.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which Article calls for securing just and humane conditions of work?</t>
+          <t>Are Directive Principles superior to Fundamental Rights?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Depends on the case</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Article 37</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Includes maternity relief provisions.</t>
+          <t>Fundamental Rights have supremacy over DPSPs.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which directive speaks about organizing agriculture and animal husbandry on modern lines?</t>
+          <t>Which Article mentions equal pay for equal work for both men and women?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Encourages scientific agriculture and animal care.</t>
+          <t>Ensures gender equality in wages.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which Article calls for just and humane conditions of work and maternity relief?</t>
+          <t>Which Article calls for the State to promote equal justice and free legal aid?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>Article 39A</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Article 40</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>Article 41</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Article 42</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Article 43</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Article 44</t>
-        </is>
-      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Ensures worker welfare.</t>
+          <t>Ensures justice for economically weak sections.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>97</v>
+        <v>4</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which Directive Principle calls for the separation of judiciary from the executive?</t>
+          <t>Which Article of the Constitution mentions the application of DPSP?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 31</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 36</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 37</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 37</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Ensures judicial independence.</t>
+          <t>States that DPSPs are non-justiciable.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which of the following Articles is related to providing just and humane conditions of work?</t>
+          <t>Which Article of the Indian Constitution directs the State to promote educational and economic interests of Scheduled Castes and Scheduled Tribes?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Also includes maternity benefits.</t>
+          <t>It aims at upliftment of SC/ST communities.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which Article calls upon the State to endeavor to promote the welfare of workers?</t>
+          <t>The Directive Principle on ‘Promotion of international peace and security’ is under which Article?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Focuses on social security and public assistance.</t>
+          <t>Guides India’s foreign policy.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a Directive Principle?</t>
+          <t>Which Article calls for just and humane conditions of work and maternity relief?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Right to Freedom of Speech</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Provision for free legal aid</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Promotion of cottage industries</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Protection of monuments</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Right to Freedom of Speech</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>This is a Fundamental Right.</t>
+          <t>Ensures worker welfare.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DPSPs are enforceable by which body?</t>
+          <t>The Directive Principle regarding the promotion of cooperative societies is mentioned in</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>High Court</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>DPSPs are non-justiciable.</t>
+          <t>Added by 97th Amendment.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which Directive Principle deals with providing adequate means of livelihood?</t>
+          <t>Who among the following is primarily responsible for implementing Directive Principles?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Article 38</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Ensures citizens have the right to work and livelihood.</t>
+          <t>The government must act according to DPSPs.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which Article requires the State to ensure the participation of workers in management?</t>
+          <t>Which of the following is not a DPSP?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Article 43A</t>
+          <t>Promotion of cottage industries</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Equal pay for equal work</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Prohibition of intoxicating drinks</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Article 43A</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Added by 42nd Amendment.</t>
+          <t>It is a Fundamental Right (Article 21A).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which Article deals with the promotion of cottage industries in rural areas?</t>
+          <t>The Directive Principle on providing adequate livelihood for citizens is found in which Article?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Encourages rural self-employment and handicrafts.</t>
+          <t>Ensures right to work and livelihood.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which Article promotes the welfare of the weaker sections of society?</t>
+          <t>Which Article provides that the State shall promote the welfare of workers?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 38</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Focuses on educational and economic interests of Scheduled Castes and Tribes.</t>
+          <t>Focuses on social security and public assistance.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which Article mandates the State to secure just and humane conditions of work?</t>
+          <t>Which Article urges the State to raise the level of nutrition and public health?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Ensures humane working conditions and maternity benefits.</t>
+          <t>Focuses on health and nutrition improvement.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What is the significance of DPSPs in governance?</t>
+          <t>Which Amendment added Article 48A on environmental protection?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>They are judicial orders</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>They limit legislative power</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>They serve as moral guidelines</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>They replace Fundamental Rights</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>They serve as moral guidelines</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Help the State frame just policies.</t>
+          <t>Inserted the directive on environment protection.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Directive Principle regarding organization of village panchayats is in</t>
+          <t>Which Article empowers the State to take steps for early childhood care?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 43A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Encourages local self-government.</t>
+          <t>Focuses on providing free and compulsory education for children below six.</t>
         </is>
       </c>
     </row>
@@ -3272,96 +3272,96 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which Article relates to the Uniform Civil Code?</t>
+          <t>Which of these is not classified under Gandhian principles?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Cottage industries</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Panchayati Raj</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Prohibition of intoxicating drinks</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Advises the State to secure a uniform civil code for citizens.</t>
+          <t>It is a Liberal-Intellectual principle.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which of these is a newly added DPSP?</t>
+          <t>Which Article promotes the welfare of the weaker sections of society?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Free legal aid</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Promotion of cooperative societies</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Uniform Civil Code</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Promotion of cooperative societies</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Inserted by 97th Amendment.</t>
+          <t>Focuses on educational and economic interests of Scheduled Castes and Tribes.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which Directive Principle relates to the promotion of scientific temper and humanism?</t>
+          <t>Which Article of the Constitution says that the State shall take steps to separate the judiciary from the executive?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Article 51A</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3371,449 +3371,449 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t>Article 49</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Article 48</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
           <t>Article 50</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Article 49</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Article 51</t>
-        </is>
-      </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Promotes rational thinking and tolerance.</t>
+          <t>Ensures independence of judiciary.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which Article promotes equal pay for equal work for both men and women?</t>
+          <t>The Directive Principle which calls for securing just and humane conditions of work is</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
+          <t>Article 44</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
           <t>Article 42</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Article 39(d)</t>
-        </is>
-      </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Ensures gender equality in wages.</t>
+          <t>Includes maternity relief provisions.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Directive Principle on providing adequate livelihood for citizens is found in which Article?</t>
+          <t>Which Directive Principle relates to the promotion of scientific temper and humanism?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Article 51A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Ensures right to work and livelihood.</t>
+          <t>Promotes rational thinking and tolerance.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Directive Principle which calls for securing just and humane conditions of work is</t>
+          <t>Which Article directs the State to ensure health and strength of workers?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
+          <t>Article 39(b)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
           <t>Article 41</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Article 42</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Article 43</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Article 44</t>
-        </is>
-      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 39(b)</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Includes maternity relief provisions.</t>
+          <t>Focuses on workers' health and strength.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which Article urges the State to organize village panchayats?</t>
+          <t>Which of the following Articles talks about separation of judiciary from executive?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Promotes decentralization through local self-government.</t>
+          <t>Separation to ensure judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which Article says that the State shall not discriminate against any citizen on grounds of religion, race, caste, sex or place of birth?</t>
+          <t>The concept of DPSP was borrowed from which country?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Article 14</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Article 15</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Article 16</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Article 17</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Article 15</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>It is a Fundamental Right, not a DPSP.</t>
+          <t>India adopted DPSP from the Irish Constitution.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Directive Principles are contained in which Part of the Constitution?</t>
+          <t>Which Article relates to the Uniform Civil Code?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Part V</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Part VI</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Comprising Articles 36 to 51.</t>
+          <t>Advises the State to secure a uniform civil code for citizens.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a Directive Principle of State Policy?</t>
+          <t>Which Article mandates the State to secure just and humane conditions of work?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Right to Property</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Promotion of cottage industries</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Uniform Civil Code</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Organization of Village Panchayats</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Right to Property</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>It was removed from Fundamental Rights and is not a DPSP.</t>
+          <t>Ensures humane working conditions and maternity benefits.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Directive Principles aim to establish</t>
+          <t>Which principle under DPSP relates to raising the standard of living and public health?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Political democracy</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Social democracy</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Religious democracy</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Economic democracy</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Social democracy</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>They promote social and economic justice.</t>
+          <t>Improves nutrition and health standards.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which Article directs the State to secure a uniform civil code?</t>
+          <t>Which principle is related to environment protection under DPSPs?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 48A</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 48A</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Promotes legal uniformity across religions.</t>
+          <t>Inserted by 42nd Amendment, directs State to protect environment.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which Article urges the State to raise the level of nutrition and public health?</t>
+          <t>Which Article in the Indian Constitution directs the State to separate the judiciary from the executive?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>Article 44</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
           <t>Article 45</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Article 46</t>
-        </is>
-      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Focuses on health and nutrition improvement.</t>
+          <t>Ensures judicial independence and impartiality.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which Article provides for the promotion of international peace and security?</t>
+          <t>Promotion of international peace and security is mentioned in which Article?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
+          <t>Article 48</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
           <t>Article 50</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>Article 51</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Article 52</t>
-        </is>
-      </c>
       <c r="F85" t="inlineStr">
         <is>
           <t>Article 53</t>
@@ -3826,272 +3826,272 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Guides India's foreign policy towards peace.</t>
+          <t>Guides India to promote global peace.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Directive Principles are</t>
+          <t>Which amendment added the Directive Principle relating to environment protection?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fundamental rights</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Non-justiciable guidelines</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Justiciable laws</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>International treaties</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Non-justiciable guidelines</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>They are guidelines for governance.</t>
+          <t>Inserted Article 48A.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which Amendment added Article 48A on environmental protection?</t>
+          <t>Which Article emphasizes the duty of the State to promote the educational and economic interests of Scheduled Castes, Scheduled Tribes, and other weaker sections?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Inserted the directive on environment protection.</t>
+          <t>Focuses on upliftment of marginalized groups.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which Article directs the State to raise the level of nutrition and public health?</t>
+          <t>Which Article deals with the promotion of cottage industries in rural areas?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
+          <t>Article 43</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Article 44</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>Article 45</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Article 46</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Article 47</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Article 48</t>
-        </is>
-      </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>It emphasizes improvement of public health.</t>
+          <t>Supports rural self-employment.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which Article directs the State to provide adequate means of livelihood to its citizens?</t>
+          <t>Which part of the Indian Constitution deals with Directive Principles of State Policy?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Part II</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Part V</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Guarantees the right to work and livelihood.</t>
+          <t>Deals with guidelines for the State in governance.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>The Directive Principle of 'Uniform Civil Code' aims to promote</t>
+          <t>Which Article says the State shall provide free legal aid?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Secularism</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Legal Uniformity</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Religious Harmony</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Federalism</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Legal Uniformity</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>To have one law for all citizens irrespective of religion.</t>
+          <t>Guarantees legal assistance for the poor.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Promotion of international peace and security is mentioned in which Article?</t>
+          <t>Which of the following is a fundamental duty, not a Directive Principle?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Promoting international peace</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Protecting environment</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Developing scientific temper</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Article 53</t>
+          <t>Respecting the Constitution</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Respecting the Constitution</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Guides India to promote global peace.</t>
+          <t>Fundamental duties are under Part IVA.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which Article mentions equal pay for equal work for both men and women?</t>
+          <t>Which Article directs the State to provide free and compulsory education to children?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4101,372 +4101,372 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Ensures gender equality in wages.</t>
+          <t>Focuses on early childhood education.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which Article states that the State shall endeavor to raise the level of nutrition and improve public health?</t>
+          <t>The Directive Principles aim to establish which type of state?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Welfare State</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Socialist State</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Secular State</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Federal State</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Welfare State</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Promotes public health initiatives.</t>
+          <t>DPSPs guide India to be a welfare state.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Who among the following is primarily responsible for implementing Directive Principles?</t>
+          <t>Which Article directs the State to secure a uniform civil code?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>The government must act according to DPSPs.</t>
+          <t>Promotes legal uniformity across religions.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which of the following is not a DPSP?</t>
+          <t>Which Article directs the State to improve public health?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Promotion of cottage industries</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Equal pay for equal work</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Prohibition of intoxicating drinks</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>It is a Fundamental Right (Article 21A).</t>
+          <t>Obliges State to raise nutrition and public health standards.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>In which case did the Supreme Court declare that DPSPs are fundamental in governance?</t>
+          <t>Which principle under DPSP reflects economic justice?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Golaknath case</t>
+          <t>Free legal aid</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Minerva Mills case</t>
+          <t>Promotion of equal justice</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Keshavananda Bharati case</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Champakam Dorairajan case</t>
+          <t>Organization of village panchayats</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Minerva Mills case</t>
+          <t>Promotion of equal justice</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Reiterated the importance of DPSPs.</t>
+          <t>Ensures fairness in law and access to courts.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which of the following is a Gandhian principle under DPSP?</t>
+          <t>Which Directive Principle calls for the separation of judiciary from the executive?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Equal pay for equal work</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Organization of Village Panchayats</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Uniform civil code</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Organization of Village Panchayats</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Reflects Gandhi’s ideals.</t>
+          <t>Ensures judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which Article directs the State to provide early childhood care and education to children below the age of six?</t>
+          <t>Which of the following is NOT a Directive Principle of State Policy?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Right to Property</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Promotion of cottage industries</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Uniform Civil Code</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Organization of Village Panchayats</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Right to Property</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Focus on child welfare.</t>
+          <t>It was removed from Fundamental Rights and is not a DPSP.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The idea of DPSP is to</t>
+          <t>Which Directive Principle mandates protection of monuments and objects of national importance?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ensure legal justice</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Ensure rule of law</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Establish a welfare state</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Limit the power of Parliament</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Establish a welfare state</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>DPSPs guide the State to build a just society.</t>
+          <t>Protects cultural heritage.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which of the following Articles talks about separation of judiciary from executive?</t>
+          <t>Which Article mandates free legal aid to ensure justice for all?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Separation to ensure judicial independence.</t>
+          <t>Ensures access to justice for the poor.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which Article directs the State to organize agriculture and animal husbandry on modern lines?</t>
+          <t>Which Article directs the State to raise the level of nutrition and public health?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
+          <t>Article 45</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Article 46</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Article 47</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t>Article 48</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Article 49</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Article 50</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Article 51</t>
-        </is>
-      </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>It encourages scientific farming and animal care.</t>
+          <t>It emphasizes improvement of public health.</t>
         </is>
       </c>
     </row>

--- a/Data/IP_DPSP.xlsx
+++ b/Data/IP_DPSP.xlsx
@@ -472,466 +472,466 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which of the following DPSPs was added by the 42nd Amendment?</t>
+          <t>Which Article empowers the State to take steps for early childhood care?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Equal pay for equal work</t>
+          <t>Article 43A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Free legal aid</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Living wage for workers</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Free legal aid</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Introduced in Article 39A.</t>
+          <t>Focuses on providing free and compulsory education for children below six.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Directive Principles are</t>
+          <t>Which Article calls for just and humane conditions of work and maternity relief?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fundamental rights</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Non-justiciable guidelines</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Justiciable laws</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>International treaties</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Non-justiciable guidelines</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>They are guidelines for governance.</t>
+          <t>Ensures worker welfare.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which of the following principles is classified as a Liberal-Intellectual Principle?</t>
+          <t>Directive Principles aim to establish</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Promotion of cooperative societies</t>
+          <t>Political democracy</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Separation of judiciary from executive</t>
+          <t>Social democracy</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Provision for early childhood care</t>
+          <t>Religious democracy</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Promotion of educational interests</t>
+          <t>Economic democracy</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Separation of judiciary from executive</t>
+          <t>Social democracy</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Aims at impartial justice system.</t>
+          <t>They promote social and economic justice.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which principle under DPSPs directs the State to protect monuments of historical importance?</t>
+          <t>Which of the following is NOT a Directive Principle?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Right to Freedom of Speech</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Provision for free legal aid</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Promotion of cottage industries</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Protection of monuments</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Right to Freedom of Speech</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Protects cultural heritage.</t>
+          <t>This is a Fundamental Right.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Directive Principles aim to establish</t>
+          <t>Which Article of the Indian Constitution directs the State to promote educational and economic interests of Scheduled Castes and Scheduled Tribes?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Political democracy</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Social democracy</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Religious democracy</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Economic democracy</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Social democracy</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>They promote social and economic justice.</t>
+          <t>It aims at upliftment of SC/ST communities.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which Article says that the State shall not discriminate against any citizen on grounds of religion, race, caste, sex or place of birth?</t>
+          <t>Which Amendment added Article 48A on environmental protection?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Article 14</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Article 15</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Article 16</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Article 17</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Article 15</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>It is a Fundamental Right, not a DPSP.</t>
+          <t>Inserted the directive on environment protection.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which Article directs the State to organize agriculture and animal husbandry on modern and scientific lines?</t>
+          <t>Which Article directs the State to provide early childhood care?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Promotes scientific agriculture.</t>
+          <t>Provision for children below 6 years.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which Directive Principle calls for free and compulsory education for children?</t>
+          <t>Which Amendment introduced the Directive Principle relating to environment protection?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Cares for early childhood education.</t>
+          <t>Added Article 48A for environmental protection.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which Article deals with the promotion of cottage industries in rural areas?</t>
+          <t>The Directive Principle regarding organization of village panchayats is in</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Article 40</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Article 42</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Article 43</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Article 44</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Article 45</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Article 46</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Encourages rural self-employment and handicrafts.</t>
+          <t>Encourages local self-government.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which Article calls upon the State to endeavor to promote the welfare of workers?</t>
+          <t>Which Article directs the State to organize agriculture and animal husbandry on modern and scientific lines?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Focuses on social security and public assistance.</t>
+          <t>Promotes scientific agriculture.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The idea of DPSP is to</t>
+          <t>Which Article calls for the State to promote equal justice and free legal aid?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ensure legal justice</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ensure rule of law</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Establish a welfare state</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Limit the power of Parliament</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Establish a welfare state</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DPSPs guide the State to build a just society.</t>
+          <t>Ensures justice for economically weak sections.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DPSPs are enforceable by which body?</t>
+          <t>Directive Principles are enforceable by</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Courts</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>High Court</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>The Executive</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -946,239 +946,239 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DPSPs are non-justiciable.</t>
+          <t>DPSPs are non-justiciable guidelines.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a Directive Principle?</t>
+          <t>Which of these is a newly added DPSP?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Right to Freedom of Speech</t>
+          <t>Free legal aid</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Provision for free legal aid</t>
+          <t>Promotion of cooperative societies</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Promotion of cottage industries</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Protection of monuments</t>
+          <t>Uniform Civil Code</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Right to Freedom of Speech</t>
+          <t>Promotion of cooperative societies</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>This is a Fundamental Right.</t>
+          <t>Inserted by 97th Amendment.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which Article provides for the promotion of international peace and security?</t>
+          <t>Directive Principles are enforceable</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Only by Supreme Court</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Only by High Courts</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>By Parliament</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Article 53</t>
+          <t>Not enforceable in courts</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Not enforceable in courts</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Guides India's foreign policy towards peace.</t>
+          <t>They guide the State but are not legally enforceable.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which Article directs the State to provide adequate means of livelihood to its citizens?</t>
+          <t>Which Article encourages the State to promote educational interests of Scheduled Castes and Tribes?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Guarantees the right to work and livelihood.</t>
+          <t>Focuses on education and economic upliftment of SCs/STs.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which Article requires the State to ensure the participation of workers in management?</t>
+          <t>Which Article directs the State to promote the educational and economic interests of Scheduled Castes and Scheduled Tribes?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Article 43A</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Article 43A</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Added by 42nd Amendment.</t>
+          <t>Uplifts marginalized communities.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which Article promotes equal pay for equal work for both men and women?</t>
+          <t>Which Article relates to the Uniform Civil Code?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Ensures gender equality in wages.</t>
+          <t>Advises the State to secure a uniform civil code for citizens.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Directive Principles are contained in which Part of the Constitution?</t>
+          <t>Which part of the Indian Constitution deals with Directive Principles of State Policy?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Part II</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>Part III</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Part IV</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Part V</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Part VI</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Part IV</t>
@@ -1186,1062 +1186,1062 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Comprising Articles 36 to 51.</t>
+          <t>Deals with guidelines for the State in governance.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Directive Principles are mainly inspired by the constitution of which country?</t>
+          <t>Which of the following is a Gandhian Principle under DPSP?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Organization of village panchayats</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Uniform civil code</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Separation of judiciary from executive</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Organization of village panchayats</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Directive Principles are based on the Irish Constitution.</t>
+          <t>Focuses on decentralization.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Directive Principles are contained in which schedule of the Constitution?</t>
+          <t>Who among the following is primarily responsible for implementing Directive Principles?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>First Schedule</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Second Schedule</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Third Schedule</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Not in any schedule</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Not in any schedule</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>They form Part IV of the Constitution.</t>
+          <t>The government must act according to DPSPs.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which Article directs the State to organize agriculture and animal husbandry on modern lines?</t>
+          <t>Which Article directs the State to improve public health?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>Article 45</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Article 46</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Article 47</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Article 48</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Article 49</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Article 50</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Article 51</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>It encourages scientific farming and animal care.</t>
+          <t>Obliges State to raise nutrition and public health standards.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which Amendment introduced the Directive Principle relating to environment protection?</t>
+          <t>Which Article provides that the State shall promote the welfare of workers?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 38</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Added Article 48A for environmental protection.</t>
+          <t>Focuses on social security and public assistance.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The principle of 'Promotion of international peace and security' is under which Article?</t>
+          <t>Which Article requires the State to ensure the participation of workers in management?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 43A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 43A</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Guides India’s foreign policy toward peace.</t>
+          <t>Added by 42nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What is the significance of DPSPs in governance?</t>
+          <t>Which of the following is a fundamental duty, not a Directive Principle?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>They are judicial orders</t>
+          <t>Promoting international peace</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>They limit legislative power</t>
+          <t>Protecting environment</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>They serve as moral guidelines</t>
+          <t>Developing scientific temper</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>They replace Fundamental Rights</t>
+          <t>Respecting the Constitution</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>They serve as moral guidelines</t>
+          <t>Respecting the Constitution</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Help the State frame just policies.</t>
+          <t>Fundamental duties are under Part IVA.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which directive speaks about organizing agriculture and animal husbandry on modern lines?</t>
+          <t>DPSPs are enforceable by which body?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>High Court</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Encourages scientific agriculture and animal care.</t>
+          <t>DPSPs are non-justiciable.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which Article encourages the promotion of cooperative societies?</t>
+          <t>The Directive Principles aim to establish which type of state?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Welfare State</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Socialist State</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Secular State</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Federal State</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Welfare State</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Inserted by the 97th Amendment.</t>
+          <t>DPSPs guide India to be a welfare state.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>In which case did the Supreme Court declare that DPSPs are fundamental in governance?</t>
+          <t>Directive Principles are contained in which Part of the Constitution?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Golaknath case</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Minerva Mills case</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Keshavananda Bharati case</t>
+          <t>Part V</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Champakam Dorairajan case</t>
+          <t>Part VI</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Minerva Mills case</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Reiterated the importance of DPSPs.</t>
+          <t>Comprising Articles 36 to 51.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Directive Principle regarding organization of village panchayats is in</t>
+          <t>Which Article calls upon the State to endeavor to promote the welfare of workers?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>Article 39</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>Article 40</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Article 41</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Article 42</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Article 43</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Article 44</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Encourages local self-government.</t>
+          <t>Focuses on social security and public assistance.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Directive Principles do NOT cover which of the following?</t>
+          <t>Which Article urges the State to raise the level of nutrition and public health?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Environmental protection</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Right to property</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Promotion of cottage industries</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Uniform Civil Code</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Right to property</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>It is a Fundamental Right until 44th amendment, then removed.</t>
+          <t>Focuses on health and nutrition improvement.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which Directive Principle deals with providing adequate means of livelihood?</t>
+          <t>The Directive Principles are classified under which part of the Constitution?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Part V</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Article 38</t>
+          <t>Part VI</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Ensures citizens have the right to work and livelihood.</t>
+          <t>Contains Articles 36 to 51.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Directive Principles are classified under which part of the Constitution?</t>
+          <t>Which principle under DPSPs directs the State to protect monuments of historical importance?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Part V</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Part VI</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Contains Articles 36 to 51.</t>
+          <t>Protects cultural heritage.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which of these is a newly added DPSP?</t>
+          <t>Which Directive Principle relates to the promotion of scientific temper and humanism?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Free legal aid</t>
+          <t>Article 51A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Promotion of cooperative societies</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Uniform Civil Code</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Promotion of cooperative societies</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Inserted by 97th Amendment.</t>
+          <t>Promotes rational thinking and tolerance.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which Article directs the State to promote voluntary formation of cooperative societies?</t>
+          <t>Which Article states that the State shall endeavor to raise the level of nutrition and improve public health?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Added by the 97th Amendment.</t>
+          <t>Promotes public health initiatives.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Directive Principle of 'Uniform Civil Code' aims to promote</t>
+          <t>Which Article of the Constitution mentions the application of DPSP?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Secularism</t>
+          <t>Article 31</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Legal Uniformity</t>
+          <t>Article 36</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Religious Harmony</t>
+          <t>Article 37</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Federalism</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Legal Uniformity</t>
+          <t>Article 37</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>To have one law for all citizens irrespective of religion.</t>
+          <t>States that DPSPs are non-justiciable.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which Article states that the State shall endeavor to raise the level of nutrition and improve public health?</t>
+          <t>Which Article calls for securing just and humane conditions of work?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 37</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Promotes public health initiatives.</t>
+          <t>Includes maternity relief provisions.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which Article urges the State to organize village panchayats?</t>
+          <t>Which Article mentions equal pay for equal work for both men and women?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>Article 39(d)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Article 42</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>Article 43</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Article 44</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Article 40</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Article 39</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Promotes decentralization through local self-government.</t>
+          <t>Ensures gender equality in wages.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Directive Principles are enforceable</t>
+          <t>The Directive Principle related to free legal aid to the poor is found in which Article?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Only by Supreme Court</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Only by High Courts</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>By Parliament</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Not enforceable in courts</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Not enforceable in courts</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>They guide the State but are not legally enforceable.</t>
+          <t>Ensures justice access to the marginalized.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Directive Principle related to free legal aid to the poor is found in which Article?</t>
+          <t>The Directive Principle which calls for securing just and humane conditions of work is</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>Article 44</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>Article 42</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Article 39A</t>
-        </is>
-      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Ensures justice access to the marginalized.</t>
+          <t>Includes maternity relief provisions.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which Article directs the State to protect monuments of historical importance?</t>
+          <t>Which Article directs the State to ensure health and strength of workers?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 39(b)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 39(b)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Preserves cultural heritage.</t>
+          <t>Focuses on workers' health and strength.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>How many Articles are there in Part IV of the Constitution?</t>
+          <t>The Directive Principle on providing adequate livelihood for citizens is found in which Article?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Articles 36–50</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Articles 30–49</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Articles 39–52</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Articles 41–53</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Articles 36–50</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Total of 15 articles dealing with DPSPs.</t>
+          <t>Ensures right to work and livelihood.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which Article directs the State to provide early childhood care and education to children below the age of six?</t>
+          <t>Which Article directs the State to provide free and compulsory education to children?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>Article 45</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Article 39</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Article 41</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>Article 44</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Article 45</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Article 46</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Article 47</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Article 45</t>
-        </is>
-      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Focus on child welfare.</t>
+          <t>Focuses on early childhood education.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DPSPs are meant for</t>
+          <t>Which of the following Articles talks about separation of judiciary from executive?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Central Government only</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>State Government only</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Both Centre and State</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Only Judiciary</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Both Centre and State</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>They apply to all levels of government.</t>
+          <t>Separation to ensure judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which Article provides the directive for equal pay for equal work for men and women?</t>
+          <t>Which principle under DPSP reflects economic justice?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>Free legal aid</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Promotion of equal justice</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Organization of village panchayats</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>Promotion of equal justice</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Promotes gender equality in wages.</t>
+          <t>Ensures fairness in law and access to courts.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which Article calls for securing just and humane conditions of work?</t>
+          <t>Which Article mandates free legal aid to ensure justice for all?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>Article 39A</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Article 40</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Article 41</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>Article 42</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Article 41</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Article 39</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Article 37</t>
-        </is>
-      </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Includes maternity relief provisions.</t>
+          <t>Ensures access to justice for the poor.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which Article directs the State to protect monuments of historical importance?</t>
+          <t>Promotion of international peace and security is mentioned in which Article?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2256,237 +2256,237 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Preservation of cultural heritage.</t>
+          <t>Guides India to promote global peace.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which Article directs the State to promote the educational and economic interests of Scheduled Castes and Scheduled Tribes?</t>
+          <t>Are Directive Principles superior to Fundamental Rights?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Depends on the case</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Uplifts marginalized communities.</t>
+          <t>Fundamental Rights have supremacy over DPSPs.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which of the following Articles is related to providing just and humane conditions of work?</t>
+          <t>Which Article directs the State to provide early childhood care and education to children below the age of six?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Also includes maternity benefits.</t>
+          <t>Focus on child welfare.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which Article encourages the State to promote educational interests of Scheduled Castes and Tribes?</t>
+          <t>Which principle under DPSP relates to raising the standard of living and public health?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>Article 47</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Article 48</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Article 46</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>Article 45</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Article 46</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Article 47</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Article 48</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Article 46</t>
-        </is>
-      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Focuses on education and economic upliftment of SCs/STs.</t>
+          <t>Improves nutrition and health standards.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which of the following is a Gandhian Principle under DPSP?</t>
+          <t>DPSPs are</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Justiciable</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Organization of village panchayats</t>
+          <t>Non-Justiciable</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Uniform civil code</t>
+          <t>Legally binding</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Separation of judiciary from executive</t>
+          <t>Fundamental Rights</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Organization of village panchayats</t>
+          <t>Non-Justiciable</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Focuses on decentralization.</t>
+          <t>They are not enforceable by courts.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Directive Principles are enforceable by</t>
+          <t>Which Article says the State shall provide free legal aid?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Courts</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>The Executive</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>DPSPs are non-justiciable guidelines.</t>
+          <t>Guarantees legal assistance for the poor.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which directive principle aims at providing free legal aid to the poor?</t>
+          <t>Which Article provides the directive for equal pay for equal work for men and women?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2501,322 +2501,322 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Ensures justice is not denied due to economic or other disabilities.</t>
+          <t>Promotes gender equality in wages.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DPSPs are</t>
+          <t>Which of the following is not a DPSP?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Justiciable</t>
+          <t>Promotion of cottage industries</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Non-Justiciable</t>
+          <t>Equal pay for equal work</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Legally binding</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fundamental Rights</t>
+          <t>Prohibition of intoxicating drinks</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Non-Justiciable</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>They are not enforceable by courts.</t>
+          <t>It is a Fundamental Right (Article 21A).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution directs the State to raise the level of nutrition and standard of living?</t>
+          <t>Which of the following principles is classified as a Liberal-Intellectual Principle?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Promotion of cooperative societies</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Separation of judiciary from executive</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Provision for early childhood care</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Promotion of educational interests</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Separation of judiciary from executive</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Focuses on improving nutrition, public health, and standard of living.</t>
+          <t>Aims at impartial justice system.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which of the following is a Gandhian principle under DPSP?</t>
+          <t>Which Article directs the State to raise the level of nutrition and public health?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Equal pay for equal work</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Organization of Village Panchayats</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Uniform civil code</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Organization of Village Panchayats</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Reflects Gandhi’s ideals.</t>
+          <t>It emphasizes improvement of public health.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Are Directive Principles superior to Fundamental Rights?</t>
+          <t>Which Article of the Constitution says that the State shall take steps to separate the judiciary from the executive?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Depends on the case</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Not mentioned</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Fundamental Rights have supremacy over DPSPs.</t>
+          <t>Ensures independence of judiciary.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which Article mentions equal pay for equal work for both men and women?</t>
+          <t>Which Article directs the State to promote voluntary formation of cooperative societies?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Ensures gender equality in wages.</t>
+          <t>Added by the 97th Amendment.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which Article calls for the State to promote equal justice and free legal aid?</t>
+          <t>Which Article directs the State to organize agriculture and animal husbandry on modern lines?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Ensures justice for economically weak sections.</t>
+          <t>It encourages scientific farming and animal care.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution mentions the application of DPSP?</t>
+          <t>Which Directive Principle calls for free and compulsory education for children?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Article 31</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Article 36</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Article 37</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Article 37</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>States that DPSPs are non-justiciable.</t>
+          <t>Cares for early childhood education.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which Article of the Indian Constitution directs the State to promote educational and economic interests of Scheduled Castes and Scheduled Tribes?</t>
+          <t>Which Article promotes the welfare of the weaker sections of society?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>Article 45</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t>Article 46</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Article 45</t>
-        </is>
-      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2826,102 +2826,102 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>It aims at upliftment of SC/ST communities.</t>
+          <t>Focuses on educational and economic interests of Scheduled Castes and Tribes.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Directive Principle on ‘Promotion of international peace and security’ is under which Article?</t>
+          <t>The concept of DPSP was borrowed from which country?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Guides India’s foreign policy.</t>
+          <t>India adopted DPSP from the Irish Constitution.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which Article calls for just and humane conditions of work and maternity relief?</t>
+          <t>Which Article directs the State to protect monuments of historical importance?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Ensures worker welfare.</t>
+          <t>Preservation of cultural heritage.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Directive Principle regarding the promotion of cooperative societies is mentioned in</t>
+          <t>Which Article deals with the promotion of cottage industries in rural areas?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2931,432 +2931,432 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>Article 45</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>Article 46</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Article 39</t>
-        </is>
-      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Added by 97th Amendment.</t>
+          <t>Encourages rural self-employment and handicrafts.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Who among the following is primarily responsible for implementing Directive Principles?</t>
+          <t>Which Article says that the State shall not discriminate against any citizen on grounds of religion, race, caste, sex or place of birth?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Article 14</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 15</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 16</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 15</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>The government must act according to DPSPs.</t>
+          <t>It is a Fundamental Right, not a DPSP.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which of the following is not a DPSP?</t>
+          <t>Which directive principle aims at providing free legal aid to the poor?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Promotion of cottage industries</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Equal pay for equal work</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Prohibition of intoxicating drinks</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>It is a Fundamental Right (Article 21A).</t>
+          <t>Ensures justice is not denied due to economic or other disabilities.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Directive Principle on providing adequate livelihood for citizens is found in which Article?</t>
+          <t>Directive Principles do NOT cover which of the following?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Environmental protection</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Right to property</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Promotion of cottage industries</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Uniform Civil Code</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Right to property</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Ensures right to work and livelihood.</t>
+          <t>It is a Fundamental Right until 44th amendment, then removed.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which Article provides that the State shall promote the welfare of workers?</t>
+          <t>The Directive Principle on ‘Promotion of international peace and security’ is under which Article?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Article 38</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Focuses on social security and public assistance.</t>
+          <t>Guides India’s foreign policy.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which Article urges the State to raise the level of nutrition and public health?</t>
+          <t>Which amendment added the Directive Principle relating to environment protection?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Focuses on health and nutrition improvement.</t>
+          <t>Inserted Article 48A.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which Amendment added Article 48A on environmental protection?</t>
+          <t>Which of the following is a Gandhian principle under DPSP?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Equal pay for equal work</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Organization of Village Panchayats</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>Uniform civil code</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Organization of Village Panchayats</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Inserted the directive on environment protection.</t>
+          <t>Reflects Gandhi’s ideals.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which Article empowers the State to take steps for early childhood care?</t>
+          <t>The Directive Principles are contained in which schedule of the Constitution?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Article 43A</t>
+          <t>First Schedule</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Second Schedule</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Third Schedule</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Not in any schedule</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Not in any schedule</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Focuses on providing free and compulsory education for children below six.</t>
+          <t>They form Part IV of the Constitution.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which Article directs the State to provide early childhood care?</t>
+          <t>Which of the following Articles is related to providing just and humane conditions of work?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
+          <t>Article 41</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Article 42</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Article 43</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>Article 44</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Article 45</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Article 46</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Article 47</t>
-        </is>
-      </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Provision for children below 6 years.</t>
+          <t>Also includes maternity benefits.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which of these is not classified under Gandhian principles?</t>
+          <t>Directive Principles are</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cottage industries</t>
+          <t>Fundamental rights</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Non-justiciable guidelines</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Panchayati Raj</t>
+          <t>Justiciable laws</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Prohibition of intoxicating drinks</t>
+          <t>International treaties</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Non-justiciable guidelines</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>It is a Liberal-Intellectual principle.</t>
+          <t>They are guidelines for governance.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which Article promotes the welfare of the weaker sections of society?</t>
+          <t>Which Article directs the State to provide adequate means of livelihood to its citizens?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Focuses on educational and economic interests of Scheduled Castes and Tribes.</t>
+          <t>Guarantees the right to work and livelihood.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution says that the State shall take steps to separate the judiciary from the executive?</t>
+          <t>Which Article provides for the promotion of international peace and security?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3371,382 +3371,382 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Ensures independence of judiciary.</t>
+          <t>Guides India's foreign policy towards peace.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Directive Principle which calls for securing just and humane conditions of work is</t>
+          <t>Which Article urges the State to organize village panchayats?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Includes maternity relief provisions.</t>
+          <t>Promotes decentralization through local self-government.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which Directive Principle relates to the promotion of scientific temper and humanism?</t>
+          <t>Which Article directs the State to secure a uniform civil code?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Article 51A</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Promotes rational thinking and tolerance.</t>
+          <t>Promotes legal uniformity across religions.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which Article directs the State to ensure health and strength of workers?</t>
+          <t>The Directive Principle of 'Uniform Civil Code' aims to promote</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Article 39(b)</t>
+          <t>Secularism</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Legal Uniformity</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Religious Harmony</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Federalism</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Article 39(b)</t>
+          <t>Legal Uniformity</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Focuses on workers' health and strength.</t>
+          <t>To have one law for all citizens irrespective of religion.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which of the following Articles talks about separation of judiciary from executive?</t>
+          <t>Which Article deals with the promotion of cottage industries in rural areas?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
+          <t>Article 43</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
           <t>Article 44</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Article 50</t>
-        </is>
-      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Separation to ensure judicial independence.</t>
+          <t>Supports rural self-employment.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The concept of DPSP was borrowed from which country?</t>
+          <t>What is the significance of DPSPs in governance?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>They are judicial orders</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>They limit legislative power</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>They serve as moral guidelines</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>They replace Fundamental Rights</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>They serve as moral guidelines</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>India adopted DPSP from the Irish Constitution.</t>
+          <t>Help the State frame just policies.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which Article relates to the Uniform Civil Code?</t>
+          <t>Which Directive Principle mandates protection of monuments and objects of national importance?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Advises the State to secure a uniform civil code for citizens.</t>
+          <t>Protects cultural heritage.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Which Article mandates the State to secure just and humane conditions of work?</t>
+          <t>Which Article emphasizes the duty of the State to promote the educational and economic interests of Scheduled Castes, Scheduled Tribes, and other weaker sections?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Ensures humane working conditions and maternity benefits.</t>
+          <t>Focuses on upliftment of marginalized groups.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which principle under DPSP relates to raising the standard of living and public health?</t>
+          <t>The idea of DPSP is to</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Ensure legal justice</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Ensure rule of law</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Establish a welfare state</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Limit the power of Parliament</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Establish a welfare state</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Improves nutrition and health standards.</t>
+          <t>DPSPs guide the State to build a just society.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which principle is related to environment protection under DPSPs?</t>
+          <t>Which Article mandates the State to secure just and humane conditions of work?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Article 48A</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Article 48A</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Inserted by 42nd Amendment, directs State to protect environment.</t>
+          <t>Ensures humane working conditions and maternity benefits.</t>
         </is>
       </c>
     </row>
@@ -3792,681 +3792,681 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Promotion of international peace and security is mentioned in which Article?</t>
+          <t>Which principle is related to environment protection under DPSPs?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 48A</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Article 53</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 48A</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Guides India to promote global peace.</t>
+          <t>Inserted by 42nd Amendment, directs State to protect environment.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Which amendment added the Directive Principle relating to environment protection?</t>
+          <t>DPSPs are meant for</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Central Government only</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>State Government only</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Both Centre and State</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>Only Judiciary</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Both Centre and State</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Inserted Article 48A.</t>
+          <t>They apply to all levels of government.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which Article emphasizes the duty of the State to promote the educational and economic interests of Scheduled Castes, Scheduled Tribes, and other weaker sections?</t>
+          <t>Which Directive Principle calls for the separation of judiciary from the executive?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Focuses on upliftment of marginalized groups.</t>
+          <t>Ensures judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which Article deals with the promotion of cottage industries in rural areas?</t>
+          <t>Which of the following DPSPs was added by the 42nd Amendment?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Equal pay for equal work</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Free legal aid</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Living wage for workers</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Free legal aid</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Supports rural self-employment.</t>
+          <t>Introduced in Article 39A.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which part of the Indian Constitution deals with Directive Principles of State Policy?</t>
+          <t>The principle of 'Promotion of international peace and security' is under which Article?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Part II</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Part V</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Deals with guidelines for the State in governance.</t>
+          <t>Guides India’s foreign policy toward peace.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which Article says the State shall provide free legal aid?</t>
+          <t>How many Articles are there in Part IV of the Constitution?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Articles 36–50</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Articles 30–49</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Articles 39–52</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Articles 41–53</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Articles 36–50</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Guarantees legal assistance for the poor.</t>
+          <t>Total of 15 articles dealing with DPSPs.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which of the following is a fundamental duty, not a Directive Principle?</t>
+          <t>The Directive Principles are mainly inspired by the constitution of which country?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Promoting international peace</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Protecting environment</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Developing scientific temper</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Respecting the Constitution</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Respecting the Constitution</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Fundamental duties are under Part IVA.</t>
+          <t>Directive Principles are based on the Irish Constitution.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which Article directs the State to provide free and compulsory education to children?</t>
+          <t>Which Article directs the State to protect monuments of historical importance?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Focuses on early childhood education.</t>
+          <t>Preserves cultural heritage.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>The Directive Principles aim to establish which type of state?</t>
+          <t>Which Directive Principle deals with providing adequate means of livelihood?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Welfare State</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Socialist State</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Secular State</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Federal State</t>
+          <t>Article 38</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Welfare State</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>DPSPs guide India to be a welfare state.</t>
+          <t>Ensures citizens have the right to work and livelihood.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which Article directs the State to secure a uniform civil code?</t>
+          <t>Which of the following is NOT a Directive Principle of State Policy?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Right to Property</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Promotion of cottage industries</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Uniform Civil Code</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Organization of Village Panchayats</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Right to Property</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Promotes legal uniformity across religions.</t>
+          <t>It was removed from Fundamental Rights and is not a DPSP.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which Article directs the State to improve public health?</t>
+          <t>In which case did the Supreme Court declare that DPSPs are fundamental in governance?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Golaknath case</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Minerva Mills case</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Keshavananda Bharati case</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Champakam Dorairajan case</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Minerva Mills case</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Obliges State to raise nutrition and public health standards.</t>
+          <t>Reiterated the importance of DPSPs.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Which principle under DPSP reflects economic justice?</t>
+          <t>Which of these is not classified under Gandhian principles?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Free legal aid</t>
+          <t>Cottage industries</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Promotion of equal justice</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>Panchayati Raj</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Prohibition of intoxicating drinks</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
           <t>Promotion of international peace</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Organization of village panchayats</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Promotion of equal justice</t>
-        </is>
-      </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Ensures fairness in law and access to courts.</t>
+          <t>It is a Liberal-Intellectual principle.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which Directive Principle calls for the separation of judiciary from the executive?</t>
+          <t>Which Article encourages the promotion of cooperative societies?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Ensures judicial independence.</t>
+          <t>Inserted by the 97th Amendment.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a Directive Principle of State Policy?</t>
+          <t>Which Article of the Constitution directs the State to raise the level of nutrition and standard of living?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Right to Property</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Promotion of cottage industries</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Uniform Civil Code</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Organization of Village Panchayats</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Right to Property</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>It was removed from Fundamental Rights and is not a DPSP.</t>
+          <t>Focuses on improving nutrition, public health, and standard of living.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which Directive Principle mandates protection of monuments and objects of national importance?</t>
+          <t>Which Article promotes equal pay for equal work for both men and women?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Protects cultural heritage.</t>
+          <t>Ensures gender equality in wages.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which Article mandates free legal aid to ensure justice for all?</t>
+          <t>Which directive speaks about organizing agriculture and animal husbandry on modern lines?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Ensures access to justice for the poor.</t>
+          <t>Encourages scientific agriculture and animal care.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which Article directs the State to raise the level of nutrition and public health?</t>
+          <t>The Directive Principle regarding the promotion of cooperative societies is mentioned in</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t>Article 44</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
           <t>Article 46</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Article 47</t>
-        </is>
-      </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>It emphasizes improvement of public health.</t>
+          <t>Added by 97th Amendment.</t>
         </is>
       </c>
     </row>

--- a/Data/IP_DPSP.xlsx
+++ b/Data/IP_DPSP.xlsx
@@ -472,626 +472,626 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which Article empowers the State to take steps for early childhood care?</t>
+          <t>Which of the following is NOT a Directive Principle?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Article 43A</t>
+          <t>Right to Freedom of Speech</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Provision for free legal aid</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Promotion of cottage industries</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Protection of monuments</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Right to Freedom of Speech</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Focuses on providing free and compulsory education for children below six.</t>
+          <t>This is a Fundamental Right.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which Article calls for just and humane conditions of work and maternity relief?</t>
+          <t>Which Article directs the State to raise the level of nutrition and public health?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Ensures worker welfare.</t>
+          <t>It emphasizes improvement of public health.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Directive Principles aim to establish</t>
+          <t>Which principle under DPSPs directs the State to protect monuments of historical importance?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Political democracy</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Social democracy</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Religious democracy</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Economic democracy</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Social democracy</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>They promote social and economic justice.</t>
+          <t>Protects cultural heritage.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a Directive Principle?</t>
+          <t>Which Article directs the State to promote voluntary formation of cooperative societies?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Right to Freedom of Speech</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Provision for free legal aid</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Promotion of cottage industries</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Protection of monuments</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Right to Freedom of Speech</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>This is a Fundamental Right.</t>
+          <t>Added by the 97th Amendment.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which Article of the Indian Constitution directs the State to promote educational and economic interests of Scheduled Castes and Scheduled Tribes?</t>
+          <t>The Directive Principles are classified under which part of the Constitution?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Part V</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Part VI</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>It aims at upliftment of SC/ST communities.</t>
+          <t>Contains Articles 36 to 51.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which Amendment added Article 48A on environmental protection?</t>
+          <t>Which Article directs the State to secure a uniform civil code?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Inserted the directive on environment protection.</t>
+          <t>Promotes legal uniformity across religions.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which Article directs the State to provide early childhood care?</t>
+          <t>Which Article of the Indian Constitution directs the State to promote educational and economic interests of Scheduled Castes and Scheduled Tribes?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Article 46</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Article 45</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Article 44</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Article 45</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Article 47</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Article 46</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Article 47</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Article 45</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Provision for children below 6 years.</t>
+          <t>It aims at upliftment of SC/ST communities.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which Amendment introduced the Directive Principle relating to environment protection?</t>
+          <t>Which directive principle aims at providing free legal aid to the poor?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Added Article 48A for environmental protection.</t>
+          <t>Ensures justice is not denied due to economic or other disabilities.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Directive Principle regarding organization of village panchayats is in</t>
+          <t>The idea of DPSP is to</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Ensure legal justice</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Ensure rule of law</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Establish a welfare state</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Limit the power of Parliament</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Establish a welfare state</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Encourages local self-government.</t>
+          <t>DPSPs guide the State to build a just society.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which Article directs the State to organize agriculture and animal husbandry on modern and scientific lines?</t>
+          <t>Which Article promotes equal pay for equal work for both men and women?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Promotes scientific agriculture.</t>
+          <t>Ensures gender equality in wages.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which Article calls for the State to promote equal justice and free legal aid?</t>
+          <t>Directive Principles are enforceable by</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Courts</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>The Executive</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Ensures justice for economically weak sections.</t>
+          <t>DPSPs are non-justiciable guidelines.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Directive Principles are enforceable by</t>
+          <t>Which Article directs the State to protect monuments of historical importance?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Courts</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>The Executive</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DPSPs are non-justiciable guidelines.</t>
+          <t>Preservation of cultural heritage.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which of these is a newly added DPSP?</t>
+          <t>Which Article emphasizes the duty of the State to promote the educational and economic interests of Scheduled Castes, Scheduled Tribes, and other weaker sections?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Free legal aid</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Promotion of cooperative societies</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Uniform Civil Code</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Promotion of cooperative societies</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Inserted by 97th Amendment.</t>
+          <t>Focuses on upliftment of marginalized groups.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Directive Principles are enforceable</t>
+          <t>What is the significance of DPSPs in governance?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Only by Supreme Court</t>
+          <t>They are judicial orders</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Only by High Courts</t>
+          <t>They limit legislative power</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>By Parliament</t>
+          <t>They serve as moral guidelines</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Not enforceable in courts</t>
+          <t>They replace Fundamental Rights</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Not enforceable in courts</t>
+          <t>They serve as moral guidelines</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>They guide the State but are not legally enforceable.</t>
+          <t>Help the State frame just policies.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which Article encourages the State to promote educational interests of Scheduled Castes and Tribes?</t>
+          <t>Which Article directs the State to organize agriculture and animal husbandry on modern and scientific lines?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>Article 51</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>Article 48</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Article 46</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Focuses on education and economic upliftment of SCs/STs.</t>
+          <t>Promotes scientific agriculture.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which Article directs the State to promote the educational and economic interests of Scheduled Castes and Scheduled Tribes?</t>
+          <t>The Directive Principle on ‘Promotion of international peace and security’ is under which Article?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1101,474 +1101,474 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Uplifts marginalized communities.</t>
+          <t>Guides India’s foreign policy.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which Article relates to the Uniform Civil Code?</t>
+          <t>Which of the following is not a DPSP?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Promotion of cottage industries</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Equal pay for equal work</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Prohibition of intoxicating drinks</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Advises the State to secure a uniform civil code for citizens.</t>
+          <t>It is a Fundamental Right (Article 21A).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which part of the Indian Constitution deals with Directive Principles of State Policy?</t>
+          <t>Who among the following is primarily responsible for implementing Directive Principles?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Part II</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Part V</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Deals with guidelines for the State in governance.</t>
+          <t>The government must act according to DPSPs.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which of the following is a Gandhian Principle under DPSP?</t>
+          <t>Which Article calls for securing just and humane conditions of work?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Organization of village panchayats</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Uniform civil code</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Separation of judiciary from executive</t>
+          <t>Article 37</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Organization of village panchayats</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Focuses on decentralization.</t>
+          <t>Includes maternity relief provisions.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Who among the following is primarily responsible for implementing Directive Principles?</t>
+          <t>Which Article urges the State to organize village panchayats?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>The government must act according to DPSPs.</t>
+          <t>Promotes decentralization through local self-government.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which Article directs the State to improve public health?</t>
+          <t>Which amendment added the Directive Principle relating to environment protection?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Obliges State to raise nutrition and public health standards.</t>
+          <t>Inserted Article 48A.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which Article provides that the State shall promote the welfare of workers?</t>
+          <t>The Directive Principle regarding organization of village panchayats is in</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Article 38</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Focuses on social security and public assistance.</t>
+          <t>Encourages local self-government.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which Article requires the State to ensure the participation of workers in management?</t>
+          <t>Which Article calls for just and humane conditions of work and maternity relief?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Article 43A</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Article 43</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>Article 44</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Article 42</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Article 43A</t>
-        </is>
-      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Added by 42nd Amendment.</t>
+          <t>Ensures worker welfare.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which of the following is a fundamental duty, not a Directive Principle?</t>
+          <t>Which of these is not classified under Gandhian principles?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Promoting international peace</t>
+          <t>Cottage industries</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Protecting environment</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Developing scientific temper</t>
+          <t>Panchayati Raj</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Respecting the Constitution</t>
+          <t>Prohibition of intoxicating drinks</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Respecting the Constitution</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fundamental duties are under Part IVA.</t>
+          <t>It is a Liberal-Intellectual principle.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DPSPs are enforceable by which body?</t>
+          <t>In which case did the Supreme Court declare that DPSPs are fundamental in governance?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Golaknath case</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>High Court</t>
+          <t>Minerva Mills case</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Keshavananda Bharati case</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Champakam Dorairajan case</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Minerva Mills case</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>DPSPs are non-justiciable.</t>
+          <t>Reiterated the importance of DPSPs.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Directive Principles aim to establish which type of state?</t>
+          <t>Which of the following is NOT a Directive Principle of State Policy?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Welfare State</t>
+          <t>Right to Property</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Socialist State</t>
+          <t>Promotion of cottage industries</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Secular State</t>
+          <t>Uniform Civil Code</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Federal State</t>
+          <t>Organization of Village Panchayats</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Welfare State</t>
+          <t>Right to Property</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>DPSPs guide India to be a welfare state.</t>
+          <t>It was removed from Fundamental Rights and is not a DPSP.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Directive Principles are contained in which Part of the Constitution?</t>
+          <t>Which Article states that the State shall endeavor to raise the level of nutrition and improve public health?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Part V</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Part VI</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Comprising Articles 36 to 51.</t>
+          <t>Promotes public health initiatives.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which Article calls upon the State to endeavor to promote the welfare of workers?</t>
+          <t>Which Directive Principle calls for free and compulsory education for children?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>Article 45</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>Article 39</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Article 40</t>
-        </is>
-      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>Article 41</t>
@@ -1576,1257 +1576,1257 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Focuses on social security and public assistance.</t>
+          <t>Cares for early childhood education.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which Article urges the State to raise the level of nutrition and public health?</t>
+          <t>Which Article relates to the Uniform Civil Code?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>Article 44</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>Article 45</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Article 46</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Article 47</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Article 48</t>
-        </is>
-      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Focuses on health and nutrition improvement.</t>
+          <t>Advises the State to secure a uniform civil code for citizens.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Directive Principles are classified under which part of the Constitution?</t>
+          <t>Which of the following principles is classified as a Liberal-Intellectual Principle?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>Promotion of cooperative societies</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Separation of judiciary from executive</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Part V</t>
+          <t>Provision for early childhood care</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Part VI</t>
+          <t>Promotion of educational interests</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Separation of judiciary from executive</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Contains Articles 36 to 51.</t>
+          <t>Aims at impartial justice system.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which principle under DPSPs directs the State to protect monuments of historical importance?</t>
+          <t>Which of these is a newly added DPSP?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Free legal aid</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Promotion of cooperative societies</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Uniform Civil Code</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Promotion of cooperative societies</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Protects cultural heritage.</t>
+          <t>Inserted by 97th Amendment.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which Directive Principle relates to the promotion of scientific temper and humanism?</t>
+          <t>Which Article deals with the promotion of cottage industries in rural areas?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Article 51A</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Promotes rational thinking and tolerance.</t>
+          <t>Encourages rural self-employment and handicrafts.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which Article states that the State shall endeavor to raise the level of nutrition and improve public health?</t>
+          <t>Which Article directs the State to organize agriculture and animal husbandry on modern lines?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>Article 51</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>Article 48</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Article 47</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Promotes public health initiatives.</t>
+          <t>It encourages scientific farming and animal care.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution mentions the application of DPSP?</t>
+          <t>Directive Principles are enforceable</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Article 31</t>
+          <t>Only by Supreme Court</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Article 36</t>
+          <t>Only by High Courts</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Article 37</t>
+          <t>By Parliament</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Not enforceable in courts</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Article 37</t>
+          <t>Not enforceable in courts</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>States that DPSPs are non-justiciable.</t>
+          <t>They guide the State but are not legally enforceable.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which Article calls for securing just and humane conditions of work?</t>
+          <t>Which Article directs the State to improve public health?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Article 37</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Includes maternity relief provisions.</t>
+          <t>Obliges State to raise nutrition and public health standards.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which Article mentions equal pay for equal work for both men and women?</t>
+          <t>Which Article of the Constitution says that the State shall take steps to separate the judiciary from the executive?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Ensures gender equality in wages.</t>
+          <t>Ensures independence of judiciary.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Directive Principle related to free legal aid to the poor is found in which Article?</t>
+          <t>Which Article provides for the promotion of international peace and security?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Ensures justice access to the marginalized.</t>
+          <t>Guides India's foreign policy towards peace.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Directive Principle which calls for securing just and humane conditions of work is</t>
+          <t>Which principle under DPSP reflects economic justice?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Free legal aid</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Promotion of equal justice</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Organization of village panchayats</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Promotion of equal justice</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Includes maternity relief provisions.</t>
+          <t>Ensures fairness in law and access to courts.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which Article directs the State to ensure health and strength of workers?</t>
+          <t>Which Article mandates free legal aid to ensure justice for all?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Article 39(b)</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>Article 40</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>Article 41</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Article 42</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Article 43</t>
-        </is>
-      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Article 39(b)</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Focuses on workers' health and strength.</t>
+          <t>Ensures access to justice for the poor.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Directive Principle on providing adequate livelihood for citizens is found in which Article?</t>
+          <t>Which Article in the Indian Constitution directs the State to separate the judiciary from the executive?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Ensures right to work and livelihood.</t>
+          <t>Ensures judicial independence and impartiality.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which Article directs the State to provide free and compulsory education to children?</t>
+          <t>Which Article of the Constitution mentions the application of DPSP?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 31</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 36</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 37</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 37</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Focuses on early childhood education.</t>
+          <t>States that DPSPs are non-justiciable.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which of the following Articles talks about separation of judiciary from executive?</t>
+          <t>The Directive Principle which calls for securing just and humane conditions of work is</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>Article 41</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Article 42</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Article 43</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>Article 44</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Article 50</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Article 51</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Article 49</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Separation to ensure judicial independence.</t>
+          <t>Includes maternity relief provisions.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which principle under DPSP reflects economic justice?</t>
+          <t>Which Article directs the State to provide adequate means of livelihood to its citizens?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Free legal aid</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Promotion of equal justice</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Organization of village panchayats</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Promotion of equal justice</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Ensures fairness in law and access to courts.</t>
+          <t>Guarantees the right to work and livelihood.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which Article mandates free legal aid to ensure justice for all?</t>
+          <t>Are Directive Principles superior to Fundamental Rights?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Depends on the case</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Ensures access to justice for the poor.</t>
+          <t>Fundamental Rights have supremacy over DPSPs.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Promotion of international peace and security is mentioned in which Article?</t>
+          <t>Which Article encourages the State to promote educational interests of Scheduled Castes and Tribes?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>Article 45</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Article 46</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Article 47</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>Article 48</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Article 50</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Article 51</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Article 53</t>
-        </is>
-      </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Guides India to promote global peace.</t>
+          <t>Focuses on education and economic upliftment of SCs/STs.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Are Directive Principles superior to Fundamental Rights?</t>
+          <t>Which Article of the Constitution directs the State to raise the level of nutrition and standard of living?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Depends on the case</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Not mentioned</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fundamental Rights have supremacy over DPSPs.</t>
+          <t>Focuses on improving nutrition, public health, and standard of living.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which Article directs the State to provide early childhood care and education to children below the age of six?</t>
+          <t>Which Article calls upon the State to endeavor to promote the welfare of workers?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Focus on child welfare.</t>
+          <t>Focuses on social security and public assistance.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which principle under DPSP relates to raising the standard of living and public health?</t>
+          <t>The Directive Principle on providing adequate livelihood for citizens is found in which Article?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 39(a)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Improves nutrition and health standards.</t>
+          <t>Ensures right to work and livelihood.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DPSPs are</t>
+          <t>Which principle is related to environment protection under DPSPs?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Justiciable</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Non-Justiciable</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Legally binding</t>
+          <t>Article 48A</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fundamental Rights</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Non-Justiciable</t>
+          <t>Article 48A</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>They are not enforceable by courts.</t>
+          <t>Inserted by 42nd Amendment, directs State to protect environment.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which Article says the State shall provide free legal aid?</t>
+          <t>How many Articles are there in Part IV of the Constitution?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Articles 36–50</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Articles 30–49</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Articles 39–52</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Articles 41–53</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Articles 36–50</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Guarantees legal assistance for the poor.</t>
+          <t>Total of 15 articles dealing with DPSPs.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which Article provides the directive for equal pay for equal work for men and women?</t>
+          <t>Which Amendment introduced the Directive Principle relating to environment protection?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Promotes gender equality in wages.</t>
+          <t>Added Article 48A for environmental protection.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which of the following is not a DPSP?</t>
+          <t>Directive Principles do NOT cover which of the following?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>Environmental protection</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Right to property</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>Promotion of cottage industries</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Equal pay for equal work</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Right to education</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Prohibition of intoxicating drinks</t>
+          <t>Uniform Civil Code</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>Right to property</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>It is a Fundamental Right (Article 21A).</t>
+          <t>It is a Fundamental Right until 44th amendment, then removed.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which of the following principles is classified as a Liberal-Intellectual Principle?</t>
+          <t>Which of the following is a Gandhian Principle under DPSP?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Promotion of cooperative societies</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>Organization of village panchayats</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Uniform civil code</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>Separation of judiciary from executive</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Provision for early childhood care</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Promotion of educational interests</t>
-        </is>
-      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Separation of judiciary from executive</t>
+          <t>Organization of village panchayats</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Aims at impartial justice system.</t>
+          <t>Focuses on decentralization.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which Article directs the State to raise the level of nutrition and public health?</t>
+          <t>Which Article says that the State shall not discriminate against any citizen on grounds of religion, race, caste, sex or place of birth?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 14</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 15</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 16</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 15</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>It emphasizes improvement of public health.</t>
+          <t>It is a Fundamental Right, not a DPSP.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution says that the State shall take steps to separate the judiciary from the executive?</t>
+          <t>Which Article mentions equal pay for equal work for both men and women?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Ensures independence of judiciary.</t>
+          <t>Ensures gender equality in wages.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which Article directs the State to promote voluntary formation of cooperative societies?</t>
+          <t>The Directive Principles are contained in which schedule of the Constitution?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>First Schedule</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Second Schedule</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Third Schedule</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Not in any schedule</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Not in any schedule</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Added by the 97th Amendment.</t>
+          <t>They form Part IV of the Constitution.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which Article directs the State to organize agriculture and animal husbandry on modern lines?</t>
+          <t>Which Article calls for the State to promote equal justice and free legal aid?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>It encourages scientific farming and animal care.</t>
+          <t>Ensures justice for economically weak sections.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which Directive Principle calls for free and compulsory education for children?</t>
+          <t>Which of the following is a Gandhian principle under DPSP?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Equal pay for equal work</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Organization of Village Panchayats</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Uniform civil code</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Organization of Village Panchayats</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Cares for early childhood education.</t>
+          <t>Reflects Gandhi’s ideals.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which Article promotes the welfare of the weaker sections of society?</t>
+          <t>Which Article requires the State to ensure the participation of workers in management?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 43A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 43A</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Focuses on educational and economic interests of Scheduled Castes and Tribes.</t>
+          <t>Added by 42nd Amendment.</t>
         </is>
       </c>
     </row>
@@ -2872,461 +2872,461 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which Article directs the State to protect monuments of historical importance?</t>
+          <t>Which directive speaks about organizing agriculture and animal husbandry on modern lines?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>Article 47</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Article 48</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>Article 49</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Article 50</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Article 51</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Article 52</t>
-        </is>
-      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Preservation of cultural heritage.</t>
+          <t>Encourages scientific agriculture and animal care.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which Article deals with the promotion of cottage industries in rural areas?</t>
+          <t>Which Article says the State shall provide free legal aid?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Encourages rural self-employment and handicrafts.</t>
+          <t>Guarantees legal assistance for the poor.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which Article says that the State shall not discriminate against any citizen on grounds of religion, race, caste, sex or place of birth?</t>
+          <t>The Directive Principle related to free legal aid to the poor is found in which Article?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Article 14</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Article 15</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Article 16</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Article 17</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Article 15</t>
+          <t>Article 39A</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>It is a Fundamental Right, not a DPSP.</t>
+          <t>Ensures justice access to the marginalized.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which directive principle aims at providing free legal aid to the poor?</t>
+          <t>Which Article urges the State to raise the level of nutrition and public health?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Article 39A</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Ensures justice is not denied due to economic or other disabilities.</t>
+          <t>Focuses on health and nutrition improvement.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Directive Principles do NOT cover which of the following?</t>
+          <t>Which Article directs the State to provide early childhood care?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Environmental protection</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Right to property</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Promotion of cottage industries</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Uniform Civil Code</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Right to property</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>It is a Fundamental Right until 44th amendment, then removed.</t>
+          <t>Provision for children below 6 years.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Directive Principle on ‘Promotion of international peace and security’ is under which Article?</t>
+          <t>Which Directive Principle calls for the separation of judiciary from the executive?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
+          <t>Article 50</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Article 49</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>Article 51</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Article 52</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>Article 50</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Article 49</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Article 48</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Article 51</t>
-        </is>
-      </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Guides India’s foreign policy.</t>
+          <t>Ensures judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which amendment added the Directive Principle relating to environment protection?</t>
+          <t>Which principle under DPSP relates to raising the standard of living and public health?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Inserted Article 48A.</t>
+          <t>Improves nutrition and health standards.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which of the following is a Gandhian principle under DPSP?</t>
+          <t>The Directive Principles are mainly inspired by the constitution of which country?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Equal pay for equal work</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Organization of Village Panchayats</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Uniform civil code</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Organization of Village Panchayats</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Reflects Gandhi’s ideals.</t>
+          <t>Directive Principles are based on the Irish Constitution.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Directive Principles are contained in which schedule of the Constitution?</t>
+          <t>Which Directive Principle relates to the promotion of scientific temper and humanism?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>First Schedule</t>
+          <t>Article 51A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Second Schedule</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Third Schedule</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Not in any schedule</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Not in any schedule</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>They form Part IV of the Constitution.</t>
+          <t>Promotes rational thinking and tolerance.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which of the following Articles is related to providing just and humane conditions of work?</t>
+          <t>DPSPs are enforceable by which body?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>High Court</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Also includes maternity benefits.</t>
+          <t>DPSPs are non-justiciable.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Directive Principles are</t>
+          <t>DPSPs are meant for</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fundamental rights</t>
+          <t>Central Government only</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Non-justiciable guidelines</t>
+          <t>State Government only</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Justiciable laws</t>
+          <t>Both Centre and State</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>International treaties</t>
+          <t>Only Judiciary</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Non-justiciable guidelines</t>
+          <t>Both Centre and State</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>They are guidelines for governance.</t>
+          <t>They apply to all levels of government.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which Article directs the State to provide adequate means of livelihood to its citizens?</t>
+          <t>Which Article provides that the State shall promote the welfare of workers?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Article 38</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3341,772 +3341,772 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Article 39(a)</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Guarantees the right to work and livelihood.</t>
+          <t>Focuses on social security and public assistance.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which Article provides for the promotion of international peace and security?</t>
+          <t>Which Article mandates the State to secure just and humane conditions of work?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Article 53</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Guides India's foreign policy towards peace.</t>
+          <t>Ensures humane working conditions and maternity benefits.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which Article urges the State to organize village panchayats?</t>
+          <t>Directive Principles are contained in which Part of the Constitution?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Part V</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Part VI</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Promotes decentralization through local self-government.</t>
+          <t>Comprising Articles 36 to 51.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which Article directs the State to secure a uniform civil code?</t>
+          <t>The principle of 'Promotion of international peace and security' is under which Article?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Promotes legal uniformity across religions.</t>
+          <t>Guides India’s foreign policy toward peace.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Directive Principle of 'Uniform Civil Code' aims to promote</t>
+          <t>Which of the following DPSPs was added by the 42nd Amendment?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Secularism</t>
+          <t>Equal pay for equal work</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Legal Uniformity</t>
+          <t>Free legal aid</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Religious Harmony</t>
+          <t>Promotion of international peace</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Federalism</t>
+          <t>Living wage for workers</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Legal Uniformity</t>
+          <t>Free legal aid</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>To have one law for all citizens irrespective of religion.</t>
+          <t>Introduced in Article 39A.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which Article deals with the promotion of cottage industries in rural areas?</t>
+          <t>Which Article directs the State to protect monuments of historical importance?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Supports rural self-employment.</t>
+          <t>Preserves cultural heritage.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>What is the significance of DPSPs in governance?</t>
+          <t>Which Article empowers the State to take steps for early childhood care?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>They are judicial orders</t>
+          <t>Article 43A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>They limit legislative power</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>They serve as moral guidelines</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>They replace Fundamental Rights</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>They serve as moral guidelines</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Help the State frame just policies.</t>
+          <t>Focuses on providing free and compulsory education for children below six.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which Directive Principle mandates protection of monuments and objects of national importance?</t>
+          <t>Which Article directs the State to promote the educational and economic interests of Scheduled Castes and Scheduled Tribes?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>Article 45</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Article 46</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Article 47</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>Article 48</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Article 49</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Article 50</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Article 51</t>
-        </is>
-      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Protects cultural heritage.</t>
+          <t>Uplifts marginalized communities.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Which Article emphasizes the duty of the State to promote the educational and economic interests of Scheduled Castes, Scheduled Tribes, and other weaker sections?</t>
+          <t>Which Article deals with the promotion of cottage industries in rural areas?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>Article 43</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Article 44</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>Article 45</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Article 46</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Article 47</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Article 48</t>
-        </is>
-      </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Focuses on upliftment of marginalized groups.</t>
+          <t>Supports rural self-employment.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The idea of DPSP is to</t>
+          <t>DPSPs are</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ensure legal justice</t>
+          <t>Justiciable</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Ensure rule of law</t>
+          <t>Non-Justiciable</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Establish a welfare state</t>
+          <t>Legally binding</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Limit the power of Parliament</t>
+          <t>Fundamental Rights</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Establish a welfare state</t>
+          <t>Non-Justiciable</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>DPSPs guide the State to build a just society.</t>
+          <t>They are not enforceable by courts.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which Article mandates the State to secure just and humane conditions of work?</t>
+          <t>The Directive Principle of 'Uniform Civil Code' aims to promote</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Secularism</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Legal Uniformity</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Article 43</t>
+          <t>Religious Harmony</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Federalism</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Legal Uniformity</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Ensures humane working conditions and maternity benefits.</t>
+          <t>To have one law for all citizens irrespective of religion.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which Article in the Indian Constitution directs the State to separate the judiciary from the executive?</t>
+          <t>Which of the following is a fundamental duty, not a Directive Principle?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Promoting international peace</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Article 45</t>
+          <t>Protecting environment</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Developing scientific temper</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Respecting the Constitution</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Respecting the Constitution</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Ensures judicial independence and impartiality.</t>
+          <t>Fundamental duties are under Part IVA.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which principle is related to environment protection under DPSPs?</t>
+          <t>Directive Principles are</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Fundamental rights</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Non-justiciable guidelines</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Article 48A</t>
+          <t>Justiciable laws</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>International treaties</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Article 48A</t>
+          <t>Non-justiciable guidelines</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Inserted by 42nd Amendment, directs State to protect environment.</t>
+          <t>They are guidelines for governance.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DPSPs are meant for</t>
+          <t>Which Directive Principle mandates protection of monuments and objects of national importance?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Central Government only</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>State Government only</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Both Centre and State</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Only Judiciary</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Both Centre and State</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>They apply to all levels of government.</t>
+          <t>Protects cultural heritage.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which Directive Principle calls for the separation of judiciary from the executive?</t>
+          <t>Which Article directs the State to provide early childhood care and education to children below the age of six?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Ensures judicial independence.</t>
+          <t>Focus on child welfare.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which of the following DPSPs was added by the 42nd Amendment?</t>
+          <t>Directive Principles aim to establish</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Equal pay for equal work</t>
+          <t>Political democracy</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Free legal aid</t>
+          <t>Social democracy</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Religious democracy</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Living wage for workers</t>
+          <t>Economic democracy</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Free legal aid</t>
+          <t>Social democracy</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Introduced in Article 39A.</t>
+          <t>They promote social and economic justice.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The principle of 'Promotion of international peace and security' is under which Article?</t>
+          <t>Which Article encourages the promotion of cooperative societies?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Guides India’s foreign policy toward peace.</t>
+          <t>Inserted by the 97th Amendment.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>How many Articles are there in Part IV of the Constitution?</t>
+          <t>Which Article provides the directive for equal pay for equal work for men and women?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Articles 36–50</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Articles 30–49</t>
+          <t>Article 40</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Articles 39–52</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Articles 41–53</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Articles 36–50</t>
+          <t>Article 39(d)</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Total of 15 articles dealing with DPSPs.</t>
+          <t>Promotes gender equality in wages.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The Directive Principles are mainly inspired by the constitution of which country?</t>
+          <t>The Directive Principle regarding the promotion of cooperative societies is mentioned in</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Article 39</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Article 43B</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Directive Principles are based on the Irish Constitution.</t>
+          <t>Added by 97th Amendment.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which Article directs the State to protect monuments of historical importance?</t>
+          <t>Which part of the Indian Constitution deals with Directive Principles of State Policy?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Part II</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Part V</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Preserves cultural heritage.</t>
+          <t>Deals with guidelines for the State in governance.</t>
         </is>
       </c>
     </row>
@@ -4152,321 +4152,321 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a Directive Principle of State Policy?</t>
+          <t>Which Amendment added Article 48A on environmental protection?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Right to Property</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Promotion of cottage industries</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Uniform Civil Code</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Organization of Village Panchayats</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Right to Property</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>It was removed from Fundamental Rights and is not a DPSP.</t>
+          <t>Inserted the directive on environment protection.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>In which case did the Supreme Court declare that DPSPs are fundamental in governance?</t>
+          <t>Promotion of international peace and security is mentioned in which Article?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Golaknath case</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Minerva Mills case</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Keshavananda Bharati case</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Champakam Dorairajan case</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Minerva Mills case</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Reiterated the importance of DPSPs.</t>
+          <t>Guides India to promote global peace.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Which of these is not classified under Gandhian principles?</t>
+          <t>Which of the following Articles talks about separation of judiciary from executive?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cottage industries</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Panchayati Raj</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Prohibition of intoxicating drinks</t>
+          <t>Article 49</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Promotion of international peace</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>It is a Liberal-Intellectual principle.</t>
+          <t>Separation to ensure judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which Article encourages the promotion of cooperative societies?</t>
+          <t>Which Article directs the State to provide free and compulsory education to children?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t>Article 39</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Article 41</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t>Article 44</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>Article 45</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Article 46</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Article 43B</t>
-        </is>
-      </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Inserted by the 97th Amendment.</t>
+          <t>Focuses on early childhood education.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution directs the State to raise the level of nutrition and standard of living?</t>
+          <t>Which of the following Articles is related to providing just and humane conditions of work?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Focuses on improving nutrition, public health, and standard of living.</t>
+          <t>Also includes maternity benefits.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which Article promotes equal pay for equal work for both men and women?</t>
+          <t>Which Article promotes the welfare of the weaker sections of society?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>Article 45</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Article 40</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Article 41</t>
+          <t>Article 47</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Article 42</t>
+          <t>Article 48</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Article 39(d)</t>
+          <t>Article 46</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Ensures gender equality in wages.</t>
+          <t>Focuses on educational and economic interests of Scheduled Castes and Tribes.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which directive speaks about organizing agriculture and animal husbandry on modern lines?</t>
+          <t>Which Article directs the State to ensure health and strength of workers?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Article 47</t>
+          <t>Article 39(b)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 41</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Article 49</t>
+          <t>Article 42</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Article 43</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Article 48</t>
+          <t>Article 39(b)</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Encourages scientific agriculture and animal care.</t>
+          <t>Focuses on workers' health and strength.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>The Directive Principle regarding the promotion of cooperative societies is mentioned in</t>
+          <t>The Directive Principles aim to establish which type of state?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Welfare State</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Socialist State</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Article 46</t>
+          <t>Secular State</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Article 39</t>
+          <t>Federal State</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Article 43B</t>
+          <t>Welfare State</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Added by 97th Amendment.</t>
+          <t>DPSPs guide India to be a welfare state.</t>
         </is>
       </c>
     </row>
